--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ КИ/дв 02,07,26 днрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ КИ/дв 02,07,26 днрсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\02,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB43F34-E96E-4BB6-8139-36B1213FD496}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1952B62A-316A-4F35-8712-4227B6803DA5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AI$117</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="270">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -1351,17 +1351,23 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="6" width="7" customWidth="1"/>
     <col min="7" max="7" width="5" style="6" customWidth="1"/>
-    <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="8" max="8" width="3" customWidth="1"/>
+    <col min="9" max="9" width="4.140625" customWidth="1"/>
     <col min="10" max="10" width="1" customWidth="1"/>
-    <col min="11" max="20" width="7" customWidth="1"/>
-    <col min="21" max="23" width="7" style="18" customWidth="1"/>
+    <col min="11" max="13" width="7" customWidth="1"/>
+    <col min="14" max="14" width="5" customWidth="1"/>
+    <col min="15" max="19" width="7" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" customWidth="1"/>
+    <col min="21" max="23" width="5.7109375" style="18" customWidth="1"/>
     <col min="24" max="24" width="11.28515625" style="18" customWidth="1"/>
     <col min="25" max="26" width="5" customWidth="1"/>
-    <col min="27" max="33" width="7" customWidth="1"/>
+    <col min="27" max="33" width="7" hidden="1" customWidth="1"/>
     <col min="34" max="34" width="15.5703125" style="29" customWidth="1"/>
     <col min="35" max="36" width="7" customWidth="1"/>
-    <col min="37" max="51" width="3" customWidth="1"/>
+    <col min="37" max="37" width="6.7109375" customWidth="1"/>
+    <col min="38" max="38" width="8.85546875" customWidth="1"/>
+    <col min="39" max="39" width="10" customWidth="1"/>
+    <col min="40" max="51" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.25">
@@ -1665,8 +1671,12 @@
         <v>268</v>
       </c>
       <c r="AK4" s="1"/>
-      <c r="AL4" s="1"/>
-      <c r="AM4" s="1"/>
+      <c r="AL4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
       <c r="AP4" s="1"/>
@@ -1792,9 +1802,18 @@
         <f>SUM(AJ6:AJ499)</f>
         <v>17385</v>
       </c>
-      <c r="AK5" s="1"/>
-      <c r="AL5" s="1"/>
-      <c r="AM5" s="1"/>
+      <c r="AK5" s="4">
+        <f>SUM(AK6:AK499)</f>
+        <v>11187.636000000006</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" ref="AL5:AM5" si="2">SUM(AL6:AL499)</f>
+        <v>17484.526827275608</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="2"/>
+        <v>3411.4142417591129</v>
+      </c>
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
@@ -1839,11 +1858,11 @@
         <v>2685.299</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" ref="L6:L37" si="2">E6-K6</f>
+        <f t="shared" ref="L6:L37" si="3">E6-K6</f>
         <v>-147.11099999999988</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" ref="M6:M37" si="3">E6-N6</f>
+        <f t="shared" ref="M6:M37" si="4">E6-N6</f>
         <v>2538.1880000000001</v>
       </c>
       <c r="N6" s="1"/>
@@ -1856,7 +1875,7 @@
         <v>293.50405456050879</v>
       </c>
       <c r="S6" s="1">
-        <f t="shared" ref="S6:S37" si="4">M6/5</f>
+        <f t="shared" ref="S6:S37" si="5">M6/5</f>
         <v>507.63760000000002</v>
       </c>
       <c r="T6" s="5">
@@ -1879,7 +1898,7 @@
         <v>12.984954621170694</v>
       </c>
       <c r="Z6" s="1">
-        <f t="shared" ref="Z6:Z37" si="5">(F6+O6+P6+Q6+R6)/S6</f>
+        <f t="shared" ref="Z6:Z37" si="6">(F6+O6+P6+Q6+R6)/S6</f>
         <v>10.462960187563331</v>
       </c>
       <c r="AA6" s="1">
@@ -1912,9 +1931,18 @@
         <f>ROUND(G6*W6,0)</f>
         <v>1000</v>
       </c>
-      <c r="AK6" s="1"/>
-      <c r="AL6" s="1"/>
-      <c r="AM6" s="1"/>
+      <c r="AK6" s="1">
+        <f>S6*G6</f>
+        <v>507.63760000000002</v>
+      </c>
+      <c r="AL6" s="1">
+        <f>P6*G6</f>
+        <v>701.4249439496906</v>
+      </c>
+      <c r="AM6" s="1">
+        <f>R6*G6</f>
+        <v>293.50405456050879</v>
+      </c>
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1"/>
@@ -1959,11 +1987,11 @@
         <v>846.9</v>
       </c>
       <c r="L7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>30.618000000000052</v>
       </c>
       <c r="M7" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>877.51800000000003</v>
       </c>
       <c r="N7" s="1"/>
@@ -1974,15 +2002,15 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>175.50360000000001</v>
       </c>
       <c r="T7" s="5">
-        <f t="shared" ref="T7:T17" si="6">12*S7-R7-Q7-P7-O7-F7</f>
+        <f t="shared" ref="T7:T17" si="7">12*S7-R7-Q7-P7-O7-F7</f>
         <v>251.00038927600008</v>
       </c>
       <c r="U7" s="5">
-        <f t="shared" ref="U7:U70" si="7">T7</f>
+        <f t="shared" ref="U7:U70" si="8">T7</f>
         <v>251.00038927600008</v>
       </c>
       <c r="V7" s="5">
@@ -1991,11 +2019,11 @@
       <c r="W7" s="5"/>
       <c r="X7" s="16"/>
       <c r="Y7" s="1">
-        <f t="shared" ref="Y7:Y70" si="8">(F7+O7+P7+Q7+R7+U7)/S7</f>
+        <f t="shared" ref="Y7:Y70" si="9">(F7+O7+P7+Q7+R7+U7)/S7</f>
         <v>12</v>
       </c>
       <c r="Z7" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10.56982768857163</v>
       </c>
       <c r="AA7" s="1">
@@ -2021,16 +2049,25 @@
       </c>
       <c r="AH7" s="20"/>
       <c r="AI7" s="1">
-        <f t="shared" ref="AI7:AI70" si="9">ROUND(G7*V7,0)</f>
+        <f t="shared" ref="AI7:AI70" si="10">ROUND(G7*V7,0)</f>
         <v>251</v>
       </c>
       <c r="AJ7" s="1">
-        <f t="shared" ref="AJ7:AJ70" si="10">ROUND(G7*W7,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AK7" s="1"/>
-      <c r="AL7" s="1"/>
-      <c r="AM7" s="1"/>
+        <f t="shared" ref="AJ7:AJ70" si="11">ROUND(G7*W7,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="1">
+        <f t="shared" ref="AK7:AK70" si="12">S7*G7</f>
+        <v>175.50360000000001</v>
+      </c>
+      <c r="AL7" s="1">
+        <f t="shared" ref="AL7:AL70" si="13">P7*G7</f>
+        <v>143.128810724</v>
+      </c>
+      <c r="AM7" s="1">
+        <f t="shared" ref="AM7:AM70" si="14">R7*G7</f>
+        <v>0</v>
+      </c>
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
       <c r="AP7" s="1"/>
@@ -2075,11 +2112,11 @@
         <v>2835.37</v>
       </c>
       <c r="L8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.51200000000017099</v>
       </c>
       <c r="M8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2604.3119999999999</v>
       </c>
       <c r="N8" s="1">
@@ -2094,11 +2131,11 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>520.86239999999998</v>
       </c>
       <c r="T8" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1799.2284111799995</v>
       </c>
       <c r="U8" s="5">
@@ -2113,11 +2150,11 @@
       </c>
       <c r="X8" s="16"/>
       <c r="Y8" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12.959946427309784</v>
       </c>
       <c r="Z8" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.5456742295469983</v>
       </c>
       <c r="AA8" s="1">
@@ -2143,16 +2180,25 @@
       </c>
       <c r="AH8" s="20"/>
       <c r="AI8" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>599</v>
       </c>
       <c r="AJ8" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1700</v>
       </c>
-      <c r="AK8" s="1"/>
-      <c r="AL8" s="1"/>
-      <c r="AM8" s="1"/>
+      <c r="AK8" s="1">
+        <f t="shared" si="12"/>
+        <v>520.86239999999998</v>
+      </c>
+      <c r="AL8" s="1">
+        <f t="shared" si="13"/>
+        <v>78.538388820000364</v>
+      </c>
+      <c r="AM8" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
@@ -2191,11 +2237,11 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N9" s="1"/>
@@ -2206,12 +2252,12 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T9" s="5"/>
       <c r="U9" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V9" s="5">
@@ -2220,11 +2266,11 @@
       <c r="W9" s="5"/>
       <c r="X9" s="16"/>
       <c r="Y9" s="1" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z9" s="1" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA9" s="1">
@@ -2250,16 +2296,25 @@
       </c>
       <c r="AH9" s="20"/>
       <c r="AI9" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ9" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK9" s="1"/>
-      <c r="AL9" s="1"/>
-      <c r="AM9" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK9" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AL9" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM9" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1"/>
@@ -2304,11 +2359,11 @@
         <v>1837</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-69</v>
       </c>
       <c r="M10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1768</v>
       </c>
       <c r="N10" s="1"/>
@@ -2319,11 +2374,11 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>353.6</v>
       </c>
       <c r="T10" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1493.2000000000007</v>
       </c>
       <c r="U10" s="5">
@@ -2339,11 +2394,11 @@
         <v>263</v>
       </c>
       <c r="Y10" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>15.695701357466062</v>
       </c>
       <c r="Z10" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.7771493212669682</v>
       </c>
       <c r="AA10" s="1">
@@ -2371,16 +2426,25 @@
         <v>260</v>
       </c>
       <c r="AI10" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>945</v>
       </c>
       <c r="AJ10" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>315</v>
       </c>
-      <c r="AK10" s="1"/>
-      <c r="AL10" s="1"/>
-      <c r="AM10" s="1"/>
+      <c r="AK10" s="1">
+        <f t="shared" si="12"/>
+        <v>159.12</v>
+      </c>
+      <c r="AL10" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM10" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1"/>
@@ -2425,11 +2489,11 @@
         <v>2946</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-104</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2752</v>
       </c>
       <c r="N11" s="1">
@@ -2444,11 +2508,11 @@
         <v>185.3618693362792</v>
       </c>
       <c r="S11" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>550.4</v>
       </c>
       <c r="T11" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1394.4546802160021</v>
       </c>
       <c r="U11" s="5">
@@ -2463,11 +2527,11 @@
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12.908430232558139</v>
       </c>
       <c r="Z11" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.4664704211191815</v>
       </c>
       <c r="AA11" s="1">
@@ -2493,16 +2557,25 @@
       </c>
       <c r="AH11" s="20"/>
       <c r="AI11" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>268</v>
       </c>
       <c r="AJ11" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>585</v>
       </c>
-      <c r="AK11" s="1"/>
-      <c r="AL11" s="1"/>
-      <c r="AM11" s="1"/>
+      <c r="AK11" s="1">
+        <f t="shared" si="12"/>
+        <v>247.68</v>
+      </c>
+      <c r="AL11" s="1">
+        <f t="shared" si="13"/>
+        <v>199.3425527014731</v>
+      </c>
+      <c r="AM11" s="1">
+        <f t="shared" si="14"/>
+        <v>83.412841201325648</v>
+      </c>
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
       <c r="AP11" s="1"/>
@@ -2547,11 +2620,11 @@
         <v>56</v>
       </c>
       <c r="L12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>56</v>
       </c>
       <c r="N12" s="1"/>
@@ -2562,12 +2635,12 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.2</v>
       </c>
       <c r="T12" s="5"/>
       <c r="U12" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V12" s="5">
@@ -2576,11 +2649,11 @@
       <c r="W12" s="5"/>
       <c r="X12" s="16"/>
       <c r="Y12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14.464285714285715</v>
       </c>
       <c r="Z12" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.464285714285715</v>
       </c>
       <c r="AA12" s="1">
@@ -2606,16 +2679,25 @@
       </c>
       <c r="AH12" s="20"/>
       <c r="AI12" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ12" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK12" s="1"/>
-      <c r="AL12" s="1"/>
-      <c r="AM12" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK12" s="1">
+        <f t="shared" si="12"/>
+        <v>1.9039999999999999</v>
+      </c>
+      <c r="AL12" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM12" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
@@ -2658,11 +2740,11 @@
         <v>44</v>
       </c>
       <c r="L13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-15</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="N13" s="1"/>
@@ -2673,15 +2755,15 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.8</v>
       </c>
       <c r="T13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>18.599999999999994</v>
       </c>
       <c r="U13" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>18.599999999999994</v>
       </c>
       <c r="V13" s="5">
@@ -2690,11 +2772,11 @@
       <c r="W13" s="5"/>
       <c r="X13" s="16"/>
       <c r="Y13" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z13" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.793103448275863</v>
       </c>
       <c r="AA13" s="1">
@@ -2720,16 +2802,25 @@
       </c>
       <c r="AH13" s="20"/>
       <c r="AI13" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="AJ13" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK13" s="1"/>
-      <c r="AL13" s="1"/>
-      <c r="AM13" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK13" s="1">
+        <f t="shared" si="12"/>
+        <v>1.74</v>
+      </c>
+      <c r="AL13" s="1">
+        <f t="shared" si="13"/>
+        <v>15.299999999999999</v>
+      </c>
+      <c r="AM13" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
@@ -2774,11 +2865,11 @@
         <v>179</v>
       </c>
       <c r="L14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-3</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>176</v>
       </c>
       <c r="N14" s="1"/>
@@ -2789,12 +2880,12 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>35.200000000000003</v>
       </c>
       <c r="T14" s="5"/>
       <c r="U14" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V14" s="5">
@@ -2803,11 +2894,11 @@
       <c r="W14" s="5"/>
       <c r="X14" s="16"/>
       <c r="Y14" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13.060758124999998</v>
       </c>
       <c r="Z14" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>13.060758124999998</v>
       </c>
       <c r="AA14" s="1">
@@ -2833,16 +2924,25 @@
       </c>
       <c r="AH14" s="20"/>
       <c r="AI14" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ14" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK14" s="1"/>
-      <c r="AL14" s="1"/>
-      <c r="AM14" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK14" s="1">
+        <f t="shared" si="12"/>
+        <v>5.9840000000000009</v>
+      </c>
+      <c r="AL14" s="1">
+        <f t="shared" si="13"/>
+        <v>5.7355766199999962</v>
+      </c>
+      <c r="AM14" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN14" s="1"/>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
@@ -2887,11 +2987,11 @@
         <v>3927.056</v>
       </c>
       <c r="L15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>76.592000000000098</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3715.8420000000001</v>
       </c>
       <c r="N15" s="1">
@@ -2908,17 +3008,17 @@
         <v>275.90390136870622</v>
       </c>
       <c r="S15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>743.16840000000002</v>
       </c>
       <c r="T15" s="5">
-        <f t="shared" si="6"/>
-        <v>1974.1413377331983</v>
-      </c>
-      <c r="U15" s="5">
         <f t="shared" si="7"/>
         <v>1974.1413377331983</v>
       </c>
+      <c r="U15" s="5">
+        <f t="shared" si="8"/>
+        <v>1974.1413377331983</v>
+      </c>
       <c r="V15" s="5">
         <v>774.14133773319827</v>
       </c>
@@ -2927,11 +3027,11 @@
       </c>
       <c r="X15" s="16"/>
       <c r="Y15" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11.999999999999998</v>
       </c>
       <c r="Z15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.3436150706445531</v>
       </c>
       <c r="AA15" s="1">
@@ -2957,16 +3057,25 @@
       </c>
       <c r="AH15" s="20"/>
       <c r="AI15" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>774</v>
       </c>
       <c r="AJ15" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1200</v>
       </c>
-      <c r="AK15" s="1"/>
-      <c r="AL15" s="1"/>
-      <c r="AM15" s="1"/>
+      <c r="AK15" s="1">
+        <f t="shared" si="12"/>
+        <v>743.16840000000002</v>
+      </c>
+      <c r="AL15" s="1">
+        <f t="shared" si="13"/>
+        <v>659.36356089809442</v>
+      </c>
+      <c r="AM15" s="1">
+        <f t="shared" si="14"/>
+        <v>275.90390136870622</v>
+      </c>
       <c r="AN15" s="1"/>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1"/>
@@ -3011,11 +3120,11 @@
         <v>3948.5250000000001</v>
       </c>
       <c r="L16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-89.320000000000164</v>
       </c>
       <c r="M16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3590.2799999999997</v>
       </c>
       <c r="N16" s="1">
@@ -3030,17 +3139,17 @@
         <v>713.66208539807997</v>
       </c>
       <c r="S16" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>718.05599999999993</v>
       </c>
       <c r="T16" s="5">
-        <f t="shared" si="6"/>
-        <v>427.82249017599861</v>
-      </c>
-      <c r="U16" s="5">
         <f t="shared" si="7"/>
         <v>427.82249017599861</v>
       </c>
+      <c r="U16" s="5">
+        <f t="shared" si="8"/>
+        <v>427.82249017599861</v>
+      </c>
       <c r="V16" s="5">
         <v>227.82249017599861</v>
       </c>
@@ -3049,11 +3158,11 @@
       </c>
       <c r="X16" s="16"/>
       <c r="Y16" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.404193419209646</v>
       </c>
       <c r="AA16" s="1">
@@ -3079,16 +3188,25 @@
       </c>
       <c r="AH16" s="20"/>
       <c r="AI16" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>228</v>
       </c>
       <c r="AJ16" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>200</v>
       </c>
-      <c r="AK16" s="1"/>
-      <c r="AL16" s="1"/>
-      <c r="AM16" s="1"/>
+      <c r="AK16" s="1">
+        <f t="shared" si="12"/>
+        <v>718.05599999999993</v>
+      </c>
+      <c r="AL16" s="1">
+        <f t="shared" si="13"/>
+        <v>1705.53142442592</v>
+      </c>
+      <c r="AM16" s="1">
+        <f t="shared" si="14"/>
+        <v>713.66208539807997</v>
+      </c>
       <c r="AN16" s="1"/>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1"/>
@@ -3133,11 +3251,11 @@
         <v>370.25</v>
       </c>
       <c r="L17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-30.771999999999991</v>
       </c>
       <c r="M17" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>339.47800000000001</v>
       </c>
       <c r="N17" s="1"/>
@@ -3150,15 +3268,15 @@
         <v>75.365236141509683</v>
       </c>
       <c r="S17" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>67.895600000000002</v>
       </c>
       <c r="T17" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>301.76082324911971</v>
       </c>
       <c r="U17" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>301.76082324911971</v>
       </c>
       <c r="V17" s="5">
@@ -3167,11 +3285,11 @@
       <c r="W17" s="5"/>
       <c r="X17" s="16"/>
       <c r="Y17" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.5555172463440963</v>
       </c>
       <c r="AA17" s="1">
@@ -3197,16 +3315,25 @@
       </c>
       <c r="AH17" s="20"/>
       <c r="AI17" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>302</v>
       </c>
       <c r="AJ17" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK17" s="1"/>
-      <c r="AL17" s="1"/>
-      <c r="AM17" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK17" s="1">
+        <f t="shared" si="12"/>
+        <v>67.895600000000002</v>
+      </c>
+      <c r="AL17" s="1">
+        <f t="shared" si="13"/>
+        <v>180.1101406093706</v>
+      </c>
+      <c r="AM17" s="1">
+        <f t="shared" si="14"/>
+        <v>75.365236141509683</v>
+      </c>
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1"/>
@@ -3243,11 +3370,11 @@
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N18" s="9"/>
@@ -3258,12 +3385,12 @@
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T18" s="11"/>
       <c r="U18" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V18" s="5">
@@ -3272,11 +3399,11 @@
       <c r="W18" s="5"/>
       <c r="X18" s="17"/>
       <c r="Y18" s="1" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z18" s="9" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA18" s="9">
@@ -3302,16 +3429,25 @@
       </c>
       <c r="AH18" s="22"/>
       <c r="AI18" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ18" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK18" s="1"/>
-      <c r="AL18" s="1"/>
-      <c r="AM18" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK18" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AL18" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM18" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1"/>
@@ -3358,11 +3494,11 @@
         <v>591.79999999999995</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-172.78399999999993</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>419.01600000000002</v>
       </c>
       <c r="N19" s="9"/>
@@ -3373,12 +3509,12 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>83.803200000000004</v>
       </c>
       <c r="T19" s="11"/>
       <c r="U19" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V19" s="5">
@@ -3387,11 +3523,11 @@
       <c r="W19" s="5"/>
       <c r="X19" s="17"/>
       <c r="Y19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-7.8887202397999109E-2</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-7.8887202397999109E-2</v>
       </c>
       <c r="AA19" s="9">
@@ -3419,16 +3555,25 @@
         <v>62</v>
       </c>
       <c r="AI19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ19" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK19" s="1"/>
-      <c r="AL19" s="1"/>
-      <c r="AM19" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK19" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AL19" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1"/>
@@ -3473,11 +3618,11 @@
         <v>2.7</v>
       </c>
       <c r="L20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.22199999999999998</v>
       </c>
       <c r="M20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4780000000000002</v>
       </c>
       <c r="N20" s="1"/>
@@ -3488,12 +3633,12 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.49560000000000004</v>
       </c>
       <c r="T20" s="5"/>
       <c r="U20" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V20" s="5">
@@ -3502,11 +3647,11 @@
       <c r="W20" s="5"/>
       <c r="X20" s="16"/>
       <c r="Y20" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>31.589991928974978</v>
       </c>
       <c r="Z20" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>31.589991928974978</v>
       </c>
       <c r="AA20" s="1">
@@ -3532,16 +3677,25 @@
       </c>
       <c r="AH20" s="20"/>
       <c r="AI20" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ20" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK20" s="1"/>
-      <c r="AL20" s="1"/>
-      <c r="AM20" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK20" s="1">
+        <f t="shared" si="12"/>
+        <v>0.49560000000000004</v>
+      </c>
+      <c r="AL20" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM20" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
@@ -3586,11 +3740,11 @@
         <v>4766.51</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>94.170000000000073</v>
       </c>
       <c r="M21" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4860.68</v>
       </c>
       <c r="N21" s="1"/>
@@ -3605,15 +3759,15 @@
         <v>634.26574438765169</v>
       </c>
       <c r="S21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>972.13600000000008</v>
       </c>
       <c r="T21" s="5">
-        <f t="shared" ref="T21" si="11">12*S21-R21-Q21-P21-O21-F21</f>
+        <f t="shared" ref="T21" si="15">12*S21-R21-Q21-P21-O21-F21</f>
         <v>3250.7976291944024</v>
       </c>
       <c r="U21" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3250.7976291944024</v>
       </c>
       <c r="V21" s="5">
@@ -3624,11 +3778,11 @@
       </c>
       <c r="X21" s="16"/>
       <c r="Y21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z21" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.656025875809144</v>
       </c>
       <c r="AA21" s="1">
@@ -3654,16 +3808,25 @@
       </c>
       <c r="AH21" s="20"/>
       <c r="AI21" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1251</v>
       </c>
       <c r="AJ21" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2000</v>
       </c>
-      <c r="AK21" s="1"/>
-      <c r="AL21" s="1"/>
-      <c r="AM21" s="1"/>
+      <c r="AK21" s="1">
+        <f t="shared" si="12"/>
+        <v>972.13600000000008</v>
+      </c>
+      <c r="AL21" s="1">
+        <f t="shared" si="13"/>
+        <v>1515.787626417947</v>
+      </c>
+      <c r="AM21" s="1">
+        <f t="shared" si="14"/>
+        <v>634.26574438765169</v>
+      </c>
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1"/>
@@ -3704,11 +3867,11 @@
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N22" s="9"/>
@@ -3719,12 +3882,12 @@
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
       <c r="S22" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T22" s="11"/>
       <c r="U22" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V22" s="5">
@@ -3733,11 +3896,11 @@
       <c r="W22" s="5"/>
       <c r="X22" s="17"/>
       <c r="Y22" s="1" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z22" s="9" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA22" s="9">
@@ -3763,16 +3926,25 @@
       </c>
       <c r="AH22" s="22"/>
       <c r="AI22" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ22" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK22" s="1"/>
-      <c r="AL22" s="1"/>
-      <c r="AM22" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK22" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AL22" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM22" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1"/>
@@ -3817,11 +3989,11 @@
         <v>529.20000000000005</v>
       </c>
       <c r="L23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-4.1410000000000764</v>
       </c>
       <c r="M23" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>525.05899999999997</v>
       </c>
       <c r="N23" s="1"/>
@@ -3834,15 +4006,15 @@
         <v>98.875973152577373</v>
       </c>
       <c r="S23" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>105.01179999999999</v>
       </c>
       <c r="T23" s="5">
-        <f t="shared" ref="T23:T63" si="12">12*S23-R23-Q23-P23-O23-F23</f>
+        <f t="shared" ref="T23:T63" si="16">12*S23-R23-Q23-P23-O23-F23</f>
         <v>430.90880965228001</v>
       </c>
       <c r="U23" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>430.90880965228001</v>
       </c>
       <c r="V23" s="5">
@@ -3853,11 +4025,11 @@
       </c>
       <c r="X23" s="16"/>
       <c r="Y23" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z23" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.896567722367581</v>
       </c>
       <c r="AA23" s="1">
@@ -3883,16 +4055,25 @@
       </c>
       <c r="AH23" s="20"/>
       <c r="AI23" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>231</v>
       </c>
       <c r="AJ23" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>200</v>
       </c>
-      <c r="AK23" s="1"/>
-      <c r="AL23" s="1"/>
-      <c r="AM23" s="1"/>
+      <c r="AK23" s="1">
+        <f t="shared" si="12"/>
+        <v>105.01179999999999</v>
+      </c>
+      <c r="AL23" s="1">
+        <f t="shared" si="13"/>
+        <v>236.29681719514249</v>
+      </c>
+      <c r="AM23" s="1">
+        <f t="shared" si="14"/>
+        <v>98.875973152577373</v>
+      </c>
       <c r="AN23" s="1"/>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1"/>
@@ -3937,11 +4118,11 @@
         <v>1405</v>
       </c>
       <c r="L24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>42.092000000000098</v>
       </c>
       <c r="M24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1447.0920000000001</v>
       </c>
       <c r="N24" s="1"/>
@@ -3954,15 +4135,15 @@
         <v>261.27432225304779</v>
       </c>
       <c r="S24" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>289.41840000000002</v>
       </c>
       <c r="T24" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>793.8911313456008</v>
       </c>
       <c r="U24" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>793.8911313456008</v>
       </c>
       <c r="V24" s="5">
@@ -3973,11 +4154,11 @@
       </c>
       <c r="X24" s="16"/>
       <c r="Y24" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z24" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.2569431268170899</v>
       </c>
       <c r="AA24" s="1">
@@ -4003,16 +4184,25 @@
       </c>
       <c r="AH24" s="20"/>
       <c r="AI24" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>394</v>
       </c>
       <c r="AJ24" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>400</v>
       </c>
-      <c r="AK24" s="1"/>
-      <c r="AL24" s="1"/>
-      <c r="AM24" s="1"/>
+      <c r="AK24" s="1">
+        <f t="shared" si="12"/>
+        <v>289.41840000000002</v>
+      </c>
+      <c r="AL24" s="1">
+        <f t="shared" si="13"/>
+        <v>624.40134640135147</v>
+      </c>
+      <c r="AM24" s="1">
+        <f t="shared" si="14"/>
+        <v>261.27432225304779</v>
+      </c>
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1"/>
@@ -4057,11 +4247,11 @@
         <v>2372.2939999999999</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-196.73799999999983</v>
       </c>
       <c r="M25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1922.662</v>
       </c>
       <c r="N25" s="1">
@@ -4074,15 +4264,15 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>384.5324</v>
       </c>
       <c r="T25" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>957.78320531000054</v>
       </c>
       <c r="U25" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>957.78320531000054</v>
       </c>
       <c r="V25" s="5">
@@ -4093,11 +4283,11 @@
       </c>
       <c r="X25" s="16"/>
       <c r="Y25" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11.999999999999996</v>
       </c>
       <c r="Z25" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.509226256851175</v>
       </c>
       <c r="AA25" s="1">
@@ -4123,16 +4313,25 @@
       </c>
       <c r="AH25" s="20"/>
       <c r="AI25" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>458</v>
       </c>
       <c r="AJ25" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>500</v>
       </c>
-      <c r="AK25" s="1"/>
-      <c r="AL25" s="1"/>
-      <c r="AM25" s="1"/>
+      <c r="AK25" s="1">
+        <f t="shared" si="12"/>
+        <v>384.5324</v>
+      </c>
+      <c r="AL25" s="1">
+        <f t="shared" si="13"/>
+        <v>146.2275946899986</v>
+      </c>
+      <c r="AM25" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1"/>
@@ -4177,11 +4376,11 @@
         <v>8</v>
       </c>
       <c r="L26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.73800000000000043</v>
       </c>
       <c r="M26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2619999999999996</v>
       </c>
       <c r="N26" s="1"/>
@@ -4192,12 +4391,12 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.4523999999999999</v>
       </c>
       <c r="T26" s="5"/>
       <c r="U26" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V26" s="5">
@@ -4206,11 +4405,11 @@
       <c r="W26" s="5"/>
       <c r="X26" s="16"/>
       <c r="Y26" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>72.396722665932259</v>
       </c>
       <c r="Z26" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>72.396722665932259</v>
       </c>
       <c r="AA26" s="1">
@@ -4238,16 +4437,25 @@
         <v>185</v>
       </c>
       <c r="AI26" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ26" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK26" s="1"/>
-      <c r="AL26" s="1"/>
-      <c r="AM26" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK26" s="1">
+        <f t="shared" si="12"/>
+        <v>1.4523999999999999</v>
+      </c>
+      <c r="AL26" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM26" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
@@ -4292,11 +4500,11 @@
         <v>1958.921</v>
       </c>
       <c r="L27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-798.05300000000011</v>
       </c>
       <c r="M27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1144.4879999999998</v>
       </c>
       <c r="N27" s="1">
@@ -4311,11 +4519,11 @@
         <v>-3500</v>
       </c>
       <c r="S27" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>228.89759999999995</v>
       </c>
       <c r="T27" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>1648.837199999999</v>
       </c>
       <c r="U27" s="5">
@@ -4331,11 +4539,11 @@
         <v>700</v>
       </c>
       <c r="Y27" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10.476011980903253</v>
       </c>
       <c r="Z27" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.7966164782854888</v>
       </c>
       <c r="AA27" s="1">
@@ -4363,16 +4571,25 @@
         <v>258</v>
       </c>
       <c r="AI27" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>700</v>
       </c>
       <c r="AJ27" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>600</v>
       </c>
-      <c r="AK27" s="1"/>
-      <c r="AL27" s="1"/>
-      <c r="AM27" s="1"/>
+      <c r="AK27" s="1">
+        <f t="shared" si="12"/>
+        <v>228.89759999999995</v>
+      </c>
+      <c r="AL27" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM27" s="1">
+        <f t="shared" si="14"/>
+        <v>-3500</v>
+      </c>
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
       <c r="AP27" s="1"/>
@@ -4417,11 +4634,11 @@
         <v>14</v>
       </c>
       <c r="L28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-4.7859999999999996</v>
       </c>
       <c r="M28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.2140000000000004</v>
       </c>
       <c r="N28" s="1"/>
@@ -4432,12 +4649,12 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.8428</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V28" s="5">
@@ -4446,11 +4663,11 @@
       <c r="W28" s="5"/>
       <c r="X28" s="16"/>
       <c r="Y28" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>59.645647927067508</v>
       </c>
       <c r="Z28" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>59.645647927067508</v>
       </c>
       <c r="AA28" s="1">
@@ -4476,16 +4693,25 @@
       </c>
       <c r="AH28" s="20"/>
       <c r="AI28" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ28" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK28" s="1"/>
-      <c r="AL28" s="1"/>
-      <c r="AM28" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK28" s="1">
+        <f t="shared" si="12"/>
+        <v>1.8428</v>
+      </c>
+      <c r="AL28" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM28" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1"/>
@@ -4530,11 +4756,11 @@
         <v>6497.6270000000004</v>
       </c>
       <c r="L29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-236.05100000000039</v>
       </c>
       <c r="M29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6261.576</v>
       </c>
       <c r="N29" s="1"/>
@@ -4549,12 +4775,12 @@
         <v>1674.1929935442281</v>
       </c>
       <c r="S29" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1252.3152</v>
       </c>
       <c r="T29" s="5"/>
       <c r="U29" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V29" s="5">
@@ -4563,11 +4789,11 @@
       <c r="W29" s="5"/>
       <c r="X29" s="16"/>
       <c r="Y29" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13.52565271633739</v>
       </c>
       <c r="Z29" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>13.52565271633739</v>
       </c>
       <c r="AA29" s="1">
@@ -4593,16 +4819,25 @@
       </c>
       <c r="AH29" s="20"/>
       <c r="AI29" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ29" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK29" s="1"/>
-      <c r="AL29" s="1"/>
-      <c r="AM29" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK29" s="1">
+        <f t="shared" si="12"/>
+        <v>1252.3152</v>
+      </c>
+      <c r="AL29" s="1">
+        <f t="shared" si="13"/>
+        <v>4001.0374930463759</v>
+      </c>
+      <c r="AM29" s="1">
+        <f t="shared" si="14"/>
+        <v>1674.1929935442281</v>
+      </c>
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
       <c r="AP29" s="1"/>
@@ -4647,11 +4882,11 @@
         <v>4360</v>
       </c>
       <c r="L30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-106</v>
       </c>
       <c r="M30" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3852</v>
       </c>
       <c r="N30" s="1">
@@ -4666,15 +4901,15 @@
         <v>237.80570799180001</v>
       </c>
       <c r="S30" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>770.4</v>
       </c>
       <c r="T30" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>2507.6789559600002</v>
       </c>
       <c r="U30" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2507.6789559600002</v>
       </c>
       <c r="V30" s="5">
@@ -4685,11 +4920,11 @@
       </c>
       <c r="X30" s="16"/>
       <c r="Y30" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z30" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.7449650104361378</v>
       </c>
       <c r="AA30" s="1">
@@ -4715,16 +4950,25 @@
       </c>
       <c r="AH30" s="20"/>
       <c r="AI30" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>403</v>
       </c>
       <c r="AJ30" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>600</v>
       </c>
-      <c r="AK30" s="1"/>
-      <c r="AL30" s="1"/>
-      <c r="AM30" s="1"/>
+      <c r="AK30" s="1">
+        <f t="shared" si="12"/>
+        <v>308.16000000000003</v>
+      </c>
+      <c r="AL30" s="1">
+        <f t="shared" si="13"/>
+        <v>227.32613441928007</v>
+      </c>
+      <c r="AM30" s="1">
+        <f t="shared" si="14"/>
+        <v>95.122283196720005</v>
+      </c>
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
       <c r="AP30" s="1"/>
@@ -4769,11 +5013,11 @@
         <v>1573</v>
       </c>
       <c r="L31" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-531</v>
       </c>
       <c r="M31" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1042</v>
       </c>
       <c r="N31" s="1"/>
@@ -4786,14 +5030,14 @@
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>208.4</v>
       </c>
       <c r="T31" s="15">
         <v>600</v>
       </c>
       <c r="U31" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="V31" s="5">
@@ -4802,11 +5046,11 @@
       <c r="W31" s="5"/>
       <c r="X31" s="16"/>
       <c r="Y31" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.7898272552783103</v>
       </c>
       <c r="Z31" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.9107485604606524</v>
       </c>
       <c r="AA31" s="1">
@@ -4834,16 +5078,25 @@
         <v>256</v>
       </c>
       <c r="AI31" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>270</v>
       </c>
       <c r="AJ31" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK31" s="1"/>
-      <c r="AL31" s="1"/>
-      <c r="AM31" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK31" s="1">
+        <f t="shared" si="12"/>
+        <v>93.78</v>
+      </c>
+      <c r="AL31" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM31" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN31" s="1"/>
       <c r="AO31" s="1"/>
       <c r="AP31" s="1"/>
@@ -4888,11 +5141,11 @@
         <v>1037</v>
       </c>
       <c r="L32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-47</v>
       </c>
       <c r="M32" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>870</v>
       </c>
       <c r="N32" s="1">
@@ -4907,15 +5160,15 @@
         <v>113.39193621599991</v>
       </c>
       <c r="S32" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>174</v>
       </c>
       <c r="T32" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>211.62055520000013</v>
       </c>
       <c r="U32" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>211.62055520000013</v>
       </c>
       <c r="V32" s="5">
@@ -4924,11 +5177,11 @@
       <c r="W32" s="5"/>
       <c r="X32" s="16"/>
       <c r="Y32" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z32" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10.783789912643677</v>
       </c>
       <c r="AA32" s="1">
@@ -4954,16 +5207,25 @@
       </c>
       <c r="AH32" s="20"/>
       <c r="AI32" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>85</v>
       </c>
       <c r="AJ32" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK32" s="1"/>
-      <c r="AL32" s="1"/>
-      <c r="AM32" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK32" s="1">
+        <f t="shared" si="12"/>
+        <v>69.600000000000009</v>
+      </c>
+      <c r="AL32" s="1">
+        <f t="shared" si="13"/>
+        <v>108.39500343359992</v>
+      </c>
+      <c r="AM32" s="1">
+        <f t="shared" si="14"/>
+        <v>45.356774486399964</v>
+      </c>
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
       <c r="AP32" s="1"/>
@@ -5008,11 +5270,11 @@
         <v>524</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-16</v>
       </c>
       <c r="M33" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>508</v>
       </c>
       <c r="N33" s="1"/>
@@ -5023,7 +5285,7 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>101.6</v>
       </c>
       <c r="T33" s="5">
@@ -5031,7 +5293,7 @@
         <v>698.89097599999991</v>
       </c>
       <c r="U33" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>698.89097599999991</v>
       </c>
       <c r="V33" s="5">
@@ -5042,11 +5304,11 @@
       </c>
       <c r="X33" s="16"/>
       <c r="Y33" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="Z33" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.1211518110236227</v>
       </c>
       <c r="AA33" s="1">
@@ -5072,16 +5334,25 @@
       </c>
       <c r="AH33" s="20"/>
       <c r="AI33" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>120</v>
       </c>
       <c r="AJ33" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>160</v>
       </c>
-      <c r="AK33" s="1"/>
-      <c r="AL33" s="1"/>
-      <c r="AM33" s="1"/>
+      <c r="AK33" s="1">
+        <f t="shared" si="12"/>
+        <v>40.64</v>
+      </c>
+      <c r="AL33" s="1">
+        <f t="shared" si="13"/>
+        <v>22.843609600000015</v>
+      </c>
+      <c r="AM33" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1"/>
       <c r="AP33" s="1"/>
@@ -5126,11 +5397,11 @@
         <v>259</v>
       </c>
       <c r="L34" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-18</v>
       </c>
       <c r="M34" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>241</v>
       </c>
       <c r="N34" s="1"/>
@@ -5141,15 +5412,15 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>48.2</v>
       </c>
       <c r="T34" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>128.07215800000017</v>
       </c>
       <c r="U34" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>128.07215800000017</v>
       </c>
       <c r="V34" s="5">
@@ -5158,11 +5429,11 @@
       <c r="W34" s="5"/>
       <c r="X34" s="16"/>
       <c r="Y34" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12.000000000000002</v>
       </c>
       <c r="Z34" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.3429012863070522</v>
       </c>
       <c r="AA34" s="1">
@@ -5188,16 +5459,25 @@
       </c>
       <c r="AH34" s="20"/>
       <c r="AI34" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="AJ34" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK34" s="1"/>
-      <c r="AL34" s="1"/>
-      <c r="AM34" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK34" s="1">
+        <f t="shared" si="12"/>
+        <v>4.82</v>
+      </c>
+      <c r="AL34" s="1">
+        <f t="shared" si="13"/>
+        <v>16.23278419999999</v>
+      </c>
+      <c r="AM34" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN34" s="1"/>
       <c r="AO34" s="1"/>
       <c r="AP34" s="1"/>
@@ -5242,11 +5522,11 @@
         <v>143</v>
       </c>
       <c r="L35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-51</v>
       </c>
       <c r="M35" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="N35" s="1"/>
@@ -5257,15 +5537,15 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>18.399999999999999</v>
       </c>
       <c r="T35" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>75.799999999999983</v>
       </c>
       <c r="U35" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>75.799999999999983</v>
       </c>
       <c r="V35" s="5">
@@ -5274,11 +5554,11 @@
       <c r="W35" s="5"/>
       <c r="X35" s="16"/>
       <c r="Y35" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z35" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.8804347826086962</v>
       </c>
       <c r="AA35" s="1">
@@ -5304,16 +5584,25 @@
       </c>
       <c r="AH35" s="20"/>
       <c r="AI35" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="AJ35" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK35" s="1"/>
-      <c r="AL35" s="1"/>
-      <c r="AM35" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK35" s="1">
+        <f t="shared" si="12"/>
+        <v>6.4399999999999995</v>
+      </c>
+      <c r="AL35" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM35" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN35" s="1"/>
       <c r="AO35" s="1"/>
       <c r="AP35" s="1"/>
@@ -5358,11 +5647,11 @@
         <v>13.8</v>
       </c>
       <c r="L36" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1.136000000000001</v>
       </c>
       <c r="M36" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12.664</v>
       </c>
       <c r="N36" s="1"/>
@@ -5373,12 +5662,12 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.5327999999999999</v>
       </c>
       <c r="T36" s="5"/>
       <c r="U36" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V36" s="5">
@@ -5387,11 +5676,11 @@
       <c r="W36" s="5"/>
       <c r="X36" s="16"/>
       <c r="Y36" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14.476073910296904</v>
       </c>
       <c r="Z36" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.476073910296904</v>
       </c>
       <c r="AA36" s="1">
@@ -5417,16 +5706,25 @@
       </c>
       <c r="AH36" s="20"/>
       <c r="AI36" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ36" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK36" s="1"/>
-      <c r="AL36" s="1"/>
-      <c r="AM36" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK36" s="1">
+        <f t="shared" si="12"/>
+        <v>2.5327999999999999</v>
+      </c>
+      <c r="AL36" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM36" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN36" s="1"/>
       <c r="AO36" s="1"/>
       <c r="AP36" s="1"/>
@@ -5471,11 +5769,11 @@
         <v>485</v>
       </c>
       <c r="L37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-12</v>
       </c>
       <c r="M37" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>401</v>
       </c>
       <c r="N37" s="1">
@@ -5490,7 +5788,7 @@
         <v>73.277999999999992</v>
       </c>
       <c r="S37" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>80.2</v>
       </c>
       <c r="T37" s="5">
@@ -5498,7 +5796,7 @@
         <v>600.79999999999995</v>
       </c>
       <c r="U37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>600.79999999999995</v>
       </c>
       <c r="V37" s="5">
@@ -5509,11 +5807,11 @@
       </c>
       <c r="X37" s="16"/>
       <c r="Y37" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10.999999999999998</v>
       </c>
       <c r="Z37" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.5087281795511216</v>
       </c>
       <c r="AA37" s="1">
@@ -5539,16 +5837,25 @@
       </c>
       <c r="AH37" s="20"/>
       <c r="AI37" s="1">
-        <f t="shared" si="9"/>
-        <v>120</v>
-      </c>
-      <c r="AJ37" s="1">
         <f t="shared" si="10"/>
         <v>120</v>
       </c>
-      <c r="AK37" s="1"/>
-      <c r="AL37" s="1"/>
-      <c r="AM37" s="1"/>
+      <c r="AJ37" s="1">
+        <f t="shared" si="11"/>
+        <v>120</v>
+      </c>
+      <c r="AK37" s="1">
+        <f t="shared" si="12"/>
+        <v>32.080000000000005</v>
+      </c>
+      <c r="AL37" s="1">
+        <f t="shared" si="13"/>
+        <v>70.048800000000014</v>
+      </c>
+      <c r="AM37" s="1">
+        <f t="shared" si="14"/>
+        <v>29.311199999999999</v>
+      </c>
       <c r="AN37" s="1"/>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1"/>
@@ -5593,11 +5900,11 @@
         <v>218</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="17">E38-K38</f>
         <v>-80</v>
       </c>
       <c r="M38" s="1">
-        <f t="shared" ref="M38:M69" si="14">E38-N38</f>
+        <f t="shared" ref="M38:M69" si="18">E38-N38</f>
         <v>138</v>
       </c>
       <c r="N38" s="1"/>
@@ -5608,12 +5915,12 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1">
-        <f t="shared" ref="S38:S69" si="15">M38/5</f>
+        <f t="shared" ref="S38:S69" si="19">M38/5</f>
         <v>27.6</v>
       </c>
       <c r="T38" s="5"/>
       <c r="U38" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V38" s="5">
@@ -5622,11 +5929,11 @@
       <c r="W38" s="5"/>
       <c r="X38" s="16"/>
       <c r="Y38" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>17.934782608695652</v>
       </c>
       <c r="Z38" s="1">
-        <f t="shared" ref="Z38:Z69" si="16">(F38+O38+P38+Q38+R38)/S38</f>
+        <f t="shared" ref="Z38:Z69" si="20">(F38+O38+P38+Q38+R38)/S38</f>
         <v>17.934782608695652</v>
       </c>
       <c r="AA38" s="1">
@@ -5652,16 +5959,25 @@
       </c>
       <c r="AH38" s="20"/>
       <c r="AI38" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ38" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK38" s="1"/>
-      <c r="AL38" s="1"/>
-      <c r="AM38" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK38" s="1">
+        <f t="shared" si="12"/>
+        <v>11.040000000000001</v>
+      </c>
+      <c r="AL38" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM38" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1"/>
@@ -5706,11 +6022,11 @@
         <v>35</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-3.0599999999999987</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>31.94</v>
       </c>
       <c r="N39" s="1"/>
@@ -5721,7 +6037,7 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>6.3879999999999999</v>
       </c>
       <c r="T39" s="5">
@@ -5729,7 +6045,7 @@
         <v>42.848400000000005</v>
       </c>
       <c r="U39" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>42.848400000000005</v>
       </c>
       <c r="V39" s="5">
@@ -5738,11 +6054,11 @@
       <c r="W39" s="5"/>
       <c r="X39" s="16"/>
       <c r="Y39" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="Z39" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>3.2923606762680016</v>
       </c>
       <c r="AA39" s="1">
@@ -5768,16 +6084,25 @@
       </c>
       <c r="AH39" s="20"/>
       <c r="AI39" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>43</v>
       </c>
       <c r="AJ39" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK39" s="1"/>
-      <c r="AL39" s="1"/>
-      <c r="AM39" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK39" s="1">
+        <f t="shared" si="12"/>
+        <v>6.3879999999999999</v>
+      </c>
+      <c r="AL39" s="1">
+        <f t="shared" si="13"/>
+        <v>7.946599999999993</v>
+      </c>
+      <c r="AM39" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1"/>
@@ -5822,11 +6147,11 @@
         <v>2351</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-25</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2326</v>
       </c>
       <c r="N40" s="1"/>
@@ -5839,7 +6164,7 @@
       </c>
       <c r="R40" s="1"/>
       <c r="S40" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>465.2</v>
       </c>
       <c r="T40" s="15"/>
@@ -5852,11 +6177,11 @@
       <c r="W40" s="5"/>
       <c r="X40" s="16"/>
       <c r="Y40" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5.2687016337059331</v>
       </c>
       <c r="Z40" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>4.1938950988822015</v>
       </c>
       <c r="AA40" s="1">
@@ -5884,16 +6209,25 @@
         <v>265</v>
       </c>
       <c r="AI40" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>175</v>
       </c>
       <c r="AJ40" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK40" s="1"/>
-      <c r="AL40" s="1"/>
-      <c r="AM40" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK40" s="1">
+        <f t="shared" si="12"/>
+        <v>162.82</v>
+      </c>
+      <c r="AL40" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM40" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1"/>
@@ -5938,11 +6272,11 @@
         <v>520</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-84</v>
       </c>
       <c r="M41" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>436</v>
       </c>
       <c r="N41" s="1"/>
@@ -5953,15 +6287,15 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>87.2</v>
       </c>
       <c r="T41" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>434.27353800000026</v>
       </c>
       <c r="U41" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>434.27353800000026</v>
       </c>
       <c r="V41" s="5">
@@ -5972,11 +6306,11 @@
       </c>
       <c r="X41" s="16"/>
       <c r="Y41" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z41" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>7.0197988761467869</v>
       </c>
       <c r="AA41" s="1">
@@ -6002,16 +6336,25 @@
       </c>
       <c r="AH41" s="20"/>
       <c r="AI41" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>94</v>
       </c>
       <c r="AJ41" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>80</v>
       </c>
-      <c r="AK41" s="1"/>
-      <c r="AL41" s="1"/>
-      <c r="AM41" s="1"/>
+      <c r="AK41" s="1">
+        <f t="shared" si="12"/>
+        <v>34.880000000000003</v>
+      </c>
+      <c r="AL41" s="1">
+        <f t="shared" si="13"/>
+        <v>36.050584799999932</v>
+      </c>
+      <c r="AM41" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN41" s="1"/>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1"/>
@@ -6056,11 +6399,11 @@
         <v>147.4</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-4.4240000000000066</v>
       </c>
       <c r="M42" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>99.734000000000009</v>
       </c>
       <c r="N42" s="1">
@@ -6073,15 +6416,15 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>19.946800000000003</v>
       </c>
       <c r="T42" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>30.152800000000013</v>
       </c>
       <c r="U42" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>30.152800000000013</v>
       </c>
       <c r="V42" s="5">
@@ -6090,11 +6433,11 @@
       <c r="W42" s="5"/>
       <c r="X42" s="16"/>
       <c r="Y42" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11.999999999999998</v>
       </c>
       <c r="Z42" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>10.488338981691298</v>
       </c>
       <c r="AA42" s="1">
@@ -6120,16 +6463,25 @@
       </c>
       <c r="AH42" s="20"/>
       <c r="AI42" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="AJ42" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK42" s="1"/>
-      <c r="AL42" s="1"/>
-      <c r="AM42" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK42" s="1">
+        <f t="shared" si="12"/>
+        <v>19.946800000000003</v>
+      </c>
+      <c r="AL42" s="1">
+        <f t="shared" si="13"/>
+        <v>32.645800000000023</v>
+      </c>
+      <c r="AM42" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN42" s="1"/>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1"/>
@@ -6174,11 +6526,11 @@
         <v>589.76</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-34.442999999999984</v>
       </c>
       <c r="M43" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>555.31700000000001</v>
       </c>
       <c r="N43" s="1"/>
@@ -6191,15 +6543,15 @@
         <v>171.6293899849075</v>
       </c>
       <c r="S43" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>111.0634</v>
       </c>
       <c r="T43" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>56.92425767827956</v>
       </c>
       <c r="U43" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>56.92425767827956</v>
       </c>
       <c r="V43" s="5">
@@ -6208,11 +6560,11 @@
       <c r="W43" s="5"/>
       <c r="X43" s="16"/>
       <c r="Y43" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z43" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>11.487461596905193</v>
       </c>
       <c r="AA43" s="1">
@@ -6238,16 +6590,25 @@
       </c>
       <c r="AH43" s="20"/>
       <c r="AI43" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>57</v>
       </c>
       <c r="AJ43" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK43" s="1"/>
-      <c r="AL43" s="1"/>
-      <c r="AM43" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK43" s="1">
+        <f t="shared" si="12"/>
+        <v>111.0634</v>
+      </c>
+      <c r="AL43" s="1">
+        <f t="shared" si="13"/>
+        <v>410.16515233681292</v>
+      </c>
+      <c r="AM43" s="1">
+        <f t="shared" si="14"/>
+        <v>171.6293899849075</v>
+      </c>
       <c r="AN43" s="1"/>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1"/>
@@ -6292,11 +6653,11 @@
         <v>514</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-15</v>
       </c>
       <c r="M44" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>499</v>
       </c>
       <c r="N44" s="1"/>
@@ -6309,15 +6670,15 @@
         <v>117.6977607</v>
       </c>
       <c r="S44" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>99.8</v>
       </c>
       <c r="T44" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>550.62453999999991</v>
       </c>
       <c r="U44" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>550.62453999999991</v>
       </c>
       <c r="V44" s="5">
@@ -6328,11 +6689,11 @@
       </c>
       <c r="X44" s="16"/>
       <c r="Y44" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z44" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>6.4827200400801619</v>
       </c>
       <c r="AA44" s="1">
@@ -6358,16 +6719,25 @@
       </c>
       <c r="AH44" s="20"/>
       <c r="AI44" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>113</v>
       </c>
       <c r="AJ44" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>135</v>
       </c>
-      <c r="AK44" s="1"/>
-      <c r="AL44" s="1"/>
-      <c r="AM44" s="1"/>
+      <c r="AK44" s="1">
+        <f t="shared" si="12"/>
+        <v>44.91</v>
+      </c>
+      <c r="AL44" s="1">
+        <f t="shared" si="13"/>
+        <v>126.57496468500005</v>
+      </c>
+      <c r="AM44" s="1">
+        <f t="shared" si="14"/>
+        <v>52.963992315000006</v>
+      </c>
       <c r="AN44" s="1"/>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1"/>
@@ -6412,11 +6782,11 @@
         <v>524</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-42</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>482</v>
       </c>
       <c r="N45" s="1"/>
@@ -6429,15 +6799,15 @@
         <v>63.202073810000002</v>
       </c>
       <c r="S45" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>96.4</v>
       </c>
       <c r="T45" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>422.55568200000016</v>
       </c>
       <c r="U45" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>422.55568200000016</v>
       </c>
       <c r="V45" s="5">
@@ -6448,11 +6818,11 @@
       </c>
       <c r="X45" s="16"/>
       <c r="Y45" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12.000000000000002</v>
       </c>
       <c r="Z45" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>7.6166423029045642</v>
       </c>
       <c r="AA45" s="1">
@@ -6478,16 +6848,25 @@
       </c>
       <c r="AH45" s="20"/>
       <c r="AI45" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>100</v>
       </c>
       <c r="AJ45" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>90</v>
       </c>
-      <c r="AK45" s="1"/>
-      <c r="AL45" s="1"/>
-      <c r="AM45" s="1"/>
+      <c r="AK45" s="1">
+        <f t="shared" si="12"/>
+        <v>43.38</v>
+      </c>
+      <c r="AL45" s="1">
+        <f t="shared" si="13"/>
+        <v>67.9690098855</v>
+      </c>
+      <c r="AM45" s="1">
+        <f t="shared" si="14"/>
+        <v>28.440933214500003</v>
+      </c>
       <c r="AN45" s="1"/>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1"/>
@@ -6532,11 +6911,11 @@
         <v>84</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-22</v>
       </c>
       <c r="M46" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>62</v>
       </c>
       <c r="N46" s="1"/>
@@ -6547,7 +6926,7 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>12.4</v>
       </c>
       <c r="T46" s="5">
@@ -6555,7 +6934,7 @@
         <v>92.600000000000009</v>
       </c>
       <c r="U46" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>92.600000000000009</v>
       </c>
       <c r="V46" s="5">
@@ -6564,11 +6943,11 @@
       <c r="W46" s="5"/>
       <c r="X46" s="16"/>
       <c r="Y46" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="Z46" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1.532258064516129</v>
       </c>
       <c r="AA46" s="1">
@@ -6594,16 +6973,25 @@
       </c>
       <c r="AH46" s="20"/>
       <c r="AI46" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
       <c r="AJ46" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK46" s="1"/>
-      <c r="AL46" s="1"/>
-      <c r="AM46" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK46" s="1">
+        <f t="shared" si="12"/>
+        <v>4.9600000000000009</v>
+      </c>
+      <c r="AL46" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM46" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN46" s="1"/>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1"/>
@@ -6648,11 +7036,11 @@
         <v>720</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-171.18600000000004</v>
       </c>
       <c r="M47" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>548.81399999999996</v>
       </c>
       <c r="N47" s="1"/>
@@ -6665,15 +7053,15 @@
         <v>72.496274195309951</v>
       </c>
       <c r="S47" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>109.7628</v>
       </c>
       <c r="T47" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>466.52851798200027</v>
       </c>
       <c r="U47" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>466.52851798200027</v>
       </c>
       <c r="V47" s="5">
@@ -6684,11 +7072,11 @@
       </c>
       <c r="X47" s="16"/>
       <c r="Y47" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12.000000000000002</v>
       </c>
       <c r="Z47" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>7.7496663898697902</v>
       </c>
       <c r="AA47" s="1">
@@ -6714,16 +7102,25 @@
       </c>
       <c r="AH47" s="20"/>
       <c r="AI47" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>267</v>
       </c>
       <c r="AJ47" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>200</v>
       </c>
-      <c r="AK47" s="1"/>
-      <c r="AL47" s="1"/>
-      <c r="AM47" s="1"/>
+      <c r="AK47" s="1">
+        <f t="shared" si="12"/>
+        <v>109.7628</v>
+      </c>
+      <c r="AL47" s="1">
+        <f t="shared" si="13"/>
+        <v>173.25380782268991</v>
+      </c>
+      <c r="AM47" s="1">
+        <f t="shared" si="14"/>
+        <v>72.496274195309951</v>
+      </c>
       <c r="AN47" s="1"/>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
@@ -6768,11 +7165,11 @@
         <v>196</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-68</v>
       </c>
       <c r="M48" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>128</v>
       </c>
       <c r="N48" s="1"/>
@@ -6783,12 +7180,12 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>25.6</v>
       </c>
       <c r="T48" s="5"/>
       <c r="U48" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V48" s="5">
@@ -6797,11 +7194,11 @@
       <c r="W48" s="5"/>
       <c r="X48" s="16"/>
       <c r="Y48" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14.7578125</v>
       </c>
       <c r="Z48" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>14.7578125</v>
       </c>
       <c r="AA48" s="1">
@@ -6827,16 +7224,25 @@
       </c>
       <c r="AH48" s="20"/>
       <c r="AI48" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ48" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK48" s="1"/>
-      <c r="AL48" s="1"/>
-      <c r="AM48" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK48" s="1">
+        <f t="shared" si="12"/>
+        <v>2.5600000000000005</v>
+      </c>
+      <c r="AL48" s="1">
+        <f t="shared" si="13"/>
+        <v>18.680000000000003</v>
+      </c>
+      <c r="AM48" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN48" s="1"/>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
@@ -6881,11 +7287,11 @@
         <v>633.85</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>3.5349999999999682</v>
       </c>
       <c r="M49" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>637.38499999999999</v>
       </c>
       <c r="N49" s="1"/>
@@ -6898,15 +7304,15 @@
         <v>100.3065207414426</v>
       </c>
       <c r="S49" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>127.477</v>
       </c>
       <c r="T49" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>583.45189579172006</v>
       </c>
       <c r="U49" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>583.45189579172006</v>
       </c>
       <c r="V49" s="5">
@@ -6917,11 +7323,11 @@
       </c>
       <c r="X49" s="16"/>
       <c r="Y49" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12.000000000000002</v>
       </c>
       <c r="Z49" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>7.4230810593933017</v>
       </c>
       <c r="AA49" s="1">
@@ -6947,16 +7353,25 @@
       </c>
       <c r="AH49" s="20"/>
       <c r="AI49" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>283</v>
       </c>
       <c r="AJ49" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>300</v>
       </c>
-      <c r="AK49" s="1"/>
-      <c r="AL49" s="1"/>
-      <c r="AM49" s="1"/>
+      <c r="AK49" s="1">
+        <f t="shared" si="12"/>
+        <v>127.477</v>
+      </c>
+      <c r="AL49" s="1">
+        <f t="shared" si="13"/>
+        <v>239.71558346683739</v>
+      </c>
+      <c r="AM49" s="1">
+        <f t="shared" si="14"/>
+        <v>100.3065207414426</v>
+      </c>
       <c r="AN49" s="1"/>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1"/>
@@ -7001,11 +7416,11 @@
         <v>39.375</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>1.5859999999999985</v>
       </c>
       <c r="M50" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>40.960999999999999</v>
       </c>
       <c r="N50" s="1"/>
@@ -7016,15 +7431,15 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>8.1921999999999997</v>
       </c>
       <c r="T50" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>52.453399999999995</v>
       </c>
       <c r="U50" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>52.453399999999995</v>
       </c>
       <c r="V50" s="5">
@@ -7033,11 +7448,11 @@
       <c r="W50" s="5"/>
       <c r="X50" s="16"/>
       <c r="Y50" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z50" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>5.5971533898098205</v>
       </c>
       <c r="AA50" s="1">
@@ -7063,16 +7478,25 @@
       </c>
       <c r="AH50" s="20"/>
       <c r="AI50" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>52</v>
       </c>
       <c r="AJ50" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK50" s="1"/>
-      <c r="AL50" s="1"/>
-      <c r="AM50" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK50" s="1">
+        <f t="shared" si="12"/>
+        <v>8.1921999999999997</v>
+      </c>
+      <c r="AL50" s="1">
+        <f t="shared" si="13"/>
+        <v>26.923000000000009</v>
+      </c>
+      <c r="AM50" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN50" s="1"/>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1"/>
@@ -7117,11 +7541,11 @@
         <v>117</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-18</v>
       </c>
       <c r="M51" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>99</v>
       </c>
       <c r="N51" s="1"/>
@@ -7132,12 +7556,12 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>19.8</v>
       </c>
       <c r="T51" s="5"/>
       <c r="U51" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V51" s="5">
@@ -7146,11 +7570,11 @@
       <c r="W51" s="5"/>
       <c r="X51" s="16"/>
       <c r="Y51" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>17.505050505050505</v>
       </c>
       <c r="Z51" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>17.505050505050505</v>
       </c>
       <c r="AA51" s="1">
@@ -7176,16 +7600,25 @@
       </c>
       <c r="AH51" s="20"/>
       <c r="AI51" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ51" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="1"/>
-      <c r="AM51" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK51" s="1">
+        <f t="shared" si="12"/>
+        <v>1.9800000000000002</v>
+      </c>
+      <c r="AL51" s="1">
+        <f t="shared" si="13"/>
+        <v>18.559999999999999</v>
+      </c>
+      <c r="AM51" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN51" s="1"/>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1"/>
@@ -7228,11 +7661,11 @@
         <v>7</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-5</v>
       </c>
       <c r="M52" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="N52" s="1"/>
@@ -7243,12 +7676,12 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.4</v>
       </c>
       <c r="T52" s="5"/>
       <c r="U52" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V52" s="5">
@@ -7257,11 +7690,11 @@
       <c r="W52" s="5"/>
       <c r="X52" s="16"/>
       <c r="Y52" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>17.5</v>
       </c>
       <c r="Z52" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>17.5</v>
       </c>
       <c r="AA52" s="1">
@@ -7287,16 +7720,25 @@
       </c>
       <c r="AH52" s="20"/>
       <c r="AI52" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ52" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK52" s="1"/>
-      <c r="AL52" s="1"/>
-      <c r="AM52" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK52" s="1">
+        <f t="shared" si="12"/>
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="AL52" s="1">
+        <f t="shared" si="13"/>
+        <v>3.2</v>
+      </c>
+      <c r="AM52" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN52" s="1"/>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1"/>
@@ -7341,11 +7783,11 @@
         <v>69.599999999999994</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-13.116999999999997</v>
       </c>
       <c r="M53" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>56.482999999999997</v>
       </c>
       <c r="N53" s="1"/>
@@ -7356,12 +7798,12 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>11.2966</v>
       </c>
       <c r="T53" s="5"/>
       <c r="U53" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V53" s="5">
@@ -7370,11 +7812,11 @@
       <c r="W53" s="5"/>
       <c r="X53" s="16"/>
       <c r="Y53" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>15.189260485455801</v>
       </c>
       <c r="Z53" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>15.189260485455801</v>
       </c>
       <c r="AA53" s="1">
@@ -7400,16 +7842,25 @@
       </c>
       <c r="AH53" s="20"/>
       <c r="AI53" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ53" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK53" s="1"/>
-      <c r="AL53" s="1"/>
-      <c r="AM53" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK53" s="1">
+        <f t="shared" si="12"/>
+        <v>11.2966</v>
+      </c>
+      <c r="AL53" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM53" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN53" s="1"/>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1"/>
@@ -7454,11 +7905,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-2.6610000000000005</v>
       </c>
       <c r="M54" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2.2389999999999999</v>
       </c>
       <c r="N54" s="1"/>
@@ -7469,12 +7920,12 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.44779999999999998</v>
       </c>
       <c r="T54" s="5"/>
       <c r="U54" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V54" s="5">
@@ -7483,11 +7934,11 @@
       <c r="W54" s="5"/>
       <c r="X54" s="16"/>
       <c r="Y54" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>143.55515855292543</v>
       </c>
       <c r="Z54" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>143.55515855292543</v>
       </c>
       <c r="AA54" s="1">
@@ -7513,16 +7964,25 @@
       </c>
       <c r="AH54" s="20"/>
       <c r="AI54" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ54" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK54" s="1"/>
-      <c r="AL54" s="1"/>
-      <c r="AM54" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK54" s="1">
+        <f t="shared" si="12"/>
+        <v>0.44779999999999998</v>
+      </c>
+      <c r="AL54" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM54" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN54" s="1"/>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1"/>
@@ -7567,11 +8027,11 @@
         <v>731</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-108</v>
       </c>
       <c r="M55" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>623</v>
       </c>
       <c r="N55" s="1"/>
@@ -7584,7 +8044,7 @@
         <v>117.53507999999999</v>
       </c>
       <c r="S55" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>124.6</v>
       </c>
       <c r="T55" s="5">
@@ -7592,7 +8052,7 @@
         <v>863.17599999999982</v>
       </c>
       <c r="U55" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>863.17599999999982</v>
       </c>
       <c r="V55" s="5">
@@ -7603,11 +8063,11 @@
       </c>
       <c r="X55" s="16"/>
       <c r="Y55" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="Z55" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>4.072423756019262</v>
       </c>
       <c r="AA55" s="1">
@@ -7633,16 +8093,25 @@
       </c>
       <c r="AH55" s="20"/>
       <c r="AI55" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>145</v>
       </c>
       <c r="AJ55" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>200</v>
       </c>
-      <c r="AK55" s="1"/>
-      <c r="AL55" s="1"/>
-      <c r="AM55" s="1"/>
+      <c r="AK55" s="1">
+        <f t="shared" si="12"/>
+        <v>49.84</v>
+      </c>
+      <c r="AL55" s="1">
+        <f t="shared" si="13"/>
+        <v>112.35556800000001</v>
+      </c>
+      <c r="AM55" s="1">
+        <f t="shared" si="14"/>
+        <v>47.014032</v>
+      </c>
       <c r="AN55" s="1"/>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1"/>
@@ -7687,11 +8156,11 @@
         <v>543</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-27</v>
       </c>
       <c r="M56" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>516</v>
       </c>
       <c r="N56" s="1"/>
@@ -7704,15 +8173,15 @@
         <v>70.018704724799989</v>
       </c>
       <c r="S56" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>103.2</v>
       </c>
       <c r="T56" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>526.04845856000009</v>
       </c>
       <c r="U56" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>526.04845856000009</v>
       </c>
       <c r="V56" s="5">
@@ -7721,11 +8190,11 @@
       <c r="W56" s="5"/>
       <c r="X56" s="16"/>
       <c r="Y56" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z56" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>6.9026312155038747</v>
       </c>
       <c r="AA56" s="1">
@@ -7751,16 +8220,25 @@
       </c>
       <c r="AH56" s="20"/>
       <c r="AI56" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>210</v>
       </c>
       <c r="AJ56" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK56" s="1"/>
-      <c r="AL56" s="1"/>
-      <c r="AM56" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK56" s="1">
+        <f t="shared" si="12"/>
+        <v>41.28</v>
+      </c>
+      <c r="AL56" s="1">
+        <f t="shared" si="13"/>
+        <v>66.933134686079995</v>
+      </c>
+      <c r="AM56" s="1">
+        <f t="shared" si="14"/>
+        <v>28.007481889919998</v>
+      </c>
       <c r="AN56" s="1"/>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1"/>
@@ -7805,11 +8283,11 @@
         <v>88</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>4.7729999999999961</v>
       </c>
       <c r="M57" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>92.772999999999996</v>
       </c>
       <c r="N57" s="1"/>
@@ -7820,7 +8298,7 @@
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>18.554600000000001</v>
       </c>
       <c r="T57" s="5">
@@ -7828,7 +8306,7 @@
         <v>129.82760000000002</v>
       </c>
       <c r="U57" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>129.82760000000002</v>
       </c>
       <c r="V57" s="5">
@@ -7837,11 +8315,11 @@
       <c r="W57" s="5"/>
       <c r="X57" s="16"/>
       <c r="Y57" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="Z57" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>4.0029426665085746</v>
       </c>
       <c r="AA57" s="1">
@@ -7867,16 +8345,25 @@
       </c>
       <c r="AH57" s="20"/>
       <c r="AI57" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>130</v>
       </c>
       <c r="AJ57" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK57" s="1"/>
-      <c r="AL57" s="1"/>
-      <c r="AM57" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK57" s="1">
+        <f t="shared" si="12"/>
+        <v>18.554600000000001</v>
+      </c>
+      <c r="AL57" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM57" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN57" s="1"/>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1"/>
@@ -7921,11 +8408,11 @@
         <v>39</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-14.594000000000001</v>
       </c>
       <c r="M58" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>24.405999999999999</v>
       </c>
       <c r="N58" s="1"/>
@@ -7936,12 +8423,12 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
       <c r="S58" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>4.8811999999999998</v>
       </c>
       <c r="T58" s="5"/>
       <c r="U58" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V58" s="5">
@@ -7950,11 +8437,11 @@
       <c r="W58" s="5"/>
       <c r="X58" s="16"/>
       <c r="Y58" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>30.087888224207166</v>
       </c>
       <c r="Z58" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>30.087888224207166</v>
       </c>
       <c r="AA58" s="1">
@@ -7980,16 +8467,25 @@
       </c>
       <c r="AH58" s="20"/>
       <c r="AI58" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ58" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK58" s="1"/>
-      <c r="AL58" s="1"/>
-      <c r="AM58" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK58" s="1">
+        <f t="shared" si="12"/>
+        <v>4.8811999999999998</v>
+      </c>
+      <c r="AL58" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM58" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN58" s="1"/>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1"/>
@@ -8034,11 +8530,11 @@
         <v>497.1</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-27.087000000000046</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>470.01299999999998</v>
       </c>
       <c r="N59" s="1"/>
@@ -8049,12 +8545,12 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
       <c r="S59" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>94.002600000000001</v>
       </c>
       <c r="T59" s="5"/>
       <c r="U59" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V59" s="5">
@@ -8063,11 +8559,11 @@
       <c r="W59" s="5"/>
       <c r="X59" s="16"/>
       <c r="Y59" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>23.986496118192477</v>
       </c>
       <c r="Z59" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>23.986496118192477</v>
       </c>
       <c r="AA59" s="1">
@@ -8093,16 +8589,25 @@
       </c>
       <c r="AH59" s="20"/>
       <c r="AI59" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ59" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK59" s="1"/>
-      <c r="AL59" s="1"/>
-      <c r="AM59" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK59" s="1">
+        <f t="shared" si="12"/>
+        <v>94.002600000000001</v>
+      </c>
+      <c r="AL59" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM59" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN59" s="1"/>
       <c r="AO59" s="1"/>
       <c r="AP59" s="1"/>
@@ -8147,11 +8652,11 @@
         <v>45.9</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-0.60000000000000142</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>45.3</v>
       </c>
       <c r="N60" s="1"/>
@@ -8162,15 +8667,15 @@
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
       <c r="S60" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>9.0599999999999987</v>
       </c>
       <c r="T60" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>13.393799999999992</v>
       </c>
       <c r="U60" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13.393799999999992</v>
       </c>
       <c r="V60" s="5">
@@ -8179,11 +8684,11 @@
       <c r="W60" s="5"/>
       <c r="X60" s="16"/>
       <c r="Y60" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12.000000000000002</v>
       </c>
       <c r="Z60" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>10.521655629139074</v>
       </c>
       <c r="AA60" s="1">
@@ -8209,16 +8714,25 @@
       </c>
       <c r="AH60" s="20"/>
       <c r="AI60" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="AJ60" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK60" s="1"/>
-      <c r="AL60" s="1"/>
-      <c r="AM60" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK60" s="1">
+        <f t="shared" si="12"/>
+        <v>9.0599999999999987</v>
+      </c>
+      <c r="AL60" s="1">
+        <f t="shared" si="13"/>
+        <v>34.527199999999993</v>
+      </c>
+      <c r="AM60" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN60" s="1"/>
       <c r="AO60" s="1"/>
       <c r="AP60" s="1"/>
@@ -8263,11 +8777,11 @@
         <v>601.4</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-28.146999999999935</v>
       </c>
       <c r="M61" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>573.25300000000004</v>
       </c>
       <c r="N61" s="1"/>
@@ -8278,11 +8792,11 @@
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
       <c r="S61" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>114.65060000000001</v>
       </c>
       <c r="T61" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>793.00720000000024</v>
       </c>
       <c r="U61" s="5">
@@ -8298,11 +8812,11 @@
         <v>-50</v>
       </c>
       <c r="Y61" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11.537663126054289</v>
       </c>
       <c r="Z61" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>5.0832703884672208</v>
       </c>
       <c r="AA61" s="1">
@@ -8328,16 +8842,25 @@
       </c>
       <c r="AH61" s="20"/>
       <c r="AI61" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>340</v>
       </c>
       <c r="AJ61" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>400</v>
       </c>
-      <c r="AK61" s="1"/>
-      <c r="AL61" s="1"/>
-      <c r="AM61" s="1"/>
+      <c r="AK61" s="1">
+        <f t="shared" si="12"/>
+        <v>114.65060000000001</v>
+      </c>
+      <c r="AL61" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM61" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN61" s="1"/>
       <c r="AO61" s="1"/>
       <c r="AP61" s="1"/>
@@ -8382,11 +8905,11 @@
         <v>470</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-3</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>467</v>
       </c>
       <c r="N62" s="1"/>
@@ -8397,12 +8920,12 @@
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
       <c r="S62" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>93.4</v>
       </c>
       <c r="T62" s="5"/>
       <c r="U62" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V62" s="5">
@@ -8411,11 +8934,11 @@
       <c r="W62" s="5"/>
       <c r="X62" s="16"/>
       <c r="Y62" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>15.809256745182012</v>
       </c>
       <c r="Z62" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>15.809256745182012</v>
       </c>
       <c r="AA62" s="1">
@@ -8441,16 +8964,25 @@
       </c>
       <c r="AH62" s="20"/>
       <c r="AI62" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ62" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK62" s="1"/>
-      <c r="AL62" s="1"/>
-      <c r="AM62" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK62" s="1">
+        <f t="shared" si="12"/>
+        <v>56.04</v>
+      </c>
+      <c r="AL62" s="1">
+        <f t="shared" si="13"/>
+        <v>55.550747999999977</v>
+      </c>
+      <c r="AM62" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN62" s="1"/>
       <c r="AO62" s="1"/>
       <c r="AP62" s="1"/>
@@ -8495,11 +9027,11 @@
         <v>468</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-6</v>
       </c>
       <c r="M63" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>462</v>
       </c>
       <c r="N63" s="1"/>
@@ -8512,11 +9044,11 @@
         <v>110.40197999999999</v>
       </c>
       <c r="S63" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>92.4</v>
       </c>
       <c r="T63" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>171.55600000000027</v>
       </c>
       <c r="U63" s="5">
@@ -8530,11 +9062,11 @@
         <v>0</v>
       </c>
       <c r="Y63" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11.766709956709958</v>
       </c>
       <c r="Z63" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>10.143333333333333</v>
       </c>
       <c r="AA63" s="1">
@@ -8560,16 +9092,25 @@
       </c>
       <c r="AH63" s="20"/>
       <c r="AI63" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>90</v>
       </c>
       <c r="AJ63" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK63" s="1"/>
-      <c r="AL63" s="1"/>
-      <c r="AM63" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK63" s="1">
+        <f t="shared" si="12"/>
+        <v>55.440000000000005</v>
+      </c>
+      <c r="AL63" s="1">
+        <f t="shared" si="13"/>
+        <v>158.30521199999998</v>
+      </c>
+      <c r="AM63" s="1">
+        <f t="shared" si="14"/>
+        <v>66.241187999999994</v>
+      </c>
       <c r="AN63" s="1"/>
       <c r="AO63" s="1"/>
       <c r="AP63" s="1"/>
@@ -8614,11 +9155,11 @@
         <v>36</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-8</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>28</v>
       </c>
       <c r="N64" s="1"/>
@@ -8629,12 +9170,12 @@
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
       <c r="S64" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>5.6</v>
       </c>
       <c r="T64" s="5"/>
       <c r="U64" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V64" s="5">
@@ -8643,11 +9184,11 @@
       <c r="W64" s="5"/>
       <c r="X64" s="16"/>
       <c r="Y64" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>31.250000000000004</v>
       </c>
       <c r="Z64" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>31.250000000000004</v>
       </c>
       <c r="AA64" s="1">
@@ -8673,16 +9214,25 @@
       </c>
       <c r="AH64" s="20"/>
       <c r="AI64" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ64" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK64" s="1"/>
-      <c r="AL64" s="1"/>
-      <c r="AM64" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK64" s="1">
+        <f t="shared" si="12"/>
+        <v>1.9599999999999997</v>
+      </c>
+      <c r="AL64" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM64" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN64" s="1"/>
       <c r="AO64" s="1"/>
       <c r="AP64" s="1"/>
@@ -8727,11 +9277,11 @@
         <v>149</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-66</v>
       </c>
       <c r="M65" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>83</v>
       </c>
       <c r="N65" s="1"/>
@@ -8742,12 +9292,12 @@
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
       <c r="S65" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>16.600000000000001</v>
       </c>
       <c r="T65" s="5"/>
       <c r="U65" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V65" s="5">
@@ -8756,11 +9306,11 @@
       <c r="W65" s="5"/>
       <c r="X65" s="16"/>
       <c r="Y65" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13.433734939759034</v>
       </c>
       <c r="Z65" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>13.433734939759034</v>
       </c>
       <c r="AA65" s="1">
@@ -8786,16 +9336,25 @@
       </c>
       <c r="AH65" s="20"/>
       <c r="AI65" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ65" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK65" s="1"/>
-      <c r="AL65" s="1"/>
-      <c r="AM65" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK65" s="1">
+        <f t="shared" si="12"/>
+        <v>6.1420000000000003</v>
+      </c>
+      <c r="AL65" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM65" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN65" s="1"/>
       <c r="AO65" s="1"/>
       <c r="AP65" s="1"/>
@@ -8836,11 +9395,11 @@
         <v>20</v>
       </c>
       <c r="L66" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-18</v>
       </c>
       <c r="M66" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="N66" s="9"/>
@@ -8849,12 +9408,12 @@
       <c r="Q66" s="9"/>
       <c r="R66" s="9"/>
       <c r="S66" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.4</v>
       </c>
       <c r="T66" s="11"/>
       <c r="U66" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V66" s="5">
@@ -8863,11 +9422,11 @@
       <c r="W66" s="5"/>
       <c r="X66" s="17"/>
       <c r="Y66" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-5</v>
       </c>
       <c r="Z66" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-5</v>
       </c>
       <c r="AA66" s="9">
@@ -8893,16 +9452,25 @@
       </c>
       <c r="AH66" s="22"/>
       <c r="AI66" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ66" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK66" s="1"/>
-      <c r="AL66" s="1"/>
-      <c r="AM66" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK66" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AL66" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM66" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN66" s="1"/>
       <c r="AO66" s="1"/>
       <c r="AP66" s="1"/>
@@ -8947,11 +9515,11 @@
         <v>229</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-5</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>224</v>
       </c>
       <c r="N67" s="1"/>
@@ -8962,11 +9530,11 @@
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
       <c r="S67" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>44.8</v>
       </c>
       <c r="T67" s="5">
-        <f t="shared" ref="T67:T116" si="17">12*S67-R67-Q67-P67-O67-F67</f>
+        <f t="shared" ref="T67:T116" si="21">12*S67-R67-Q67-P67-O67-F67</f>
         <v>98.999999999999829</v>
       </c>
       <c r="U67" s="5">
@@ -8980,11 +9548,11 @@
         <v>262</v>
       </c>
       <c r="Y67" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>38.808035714285722</v>
       </c>
       <c r="Z67" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>9.790178571428573</v>
       </c>
       <c r="AA67" s="1">
@@ -9012,16 +9580,25 @@
         <v>264</v>
       </c>
       <c r="AI67" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>780</v>
       </c>
       <c r="AJ67" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK67" s="1"/>
-      <c r="AL67" s="1"/>
-      <c r="AM67" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK67" s="1">
+        <f t="shared" si="12"/>
+        <v>26.88</v>
+      </c>
+      <c r="AL67" s="1">
+        <f t="shared" si="13"/>
+        <v>73.560000000000059</v>
+      </c>
+      <c r="AM67" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN67" s="1"/>
       <c r="AO67" s="1"/>
       <c r="AP67" s="1"/>
@@ -9066,11 +9643,11 @@
         <v>121</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-24</v>
       </c>
       <c r="M68" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>97</v>
       </c>
       <c r="N68" s="1"/>
@@ -9081,7 +9658,7 @@
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
       <c r="S68" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>19.399999999999999</v>
       </c>
       <c r="T68" s="5">
@@ -9089,7 +9666,7 @@
         <v>128</v>
       </c>
       <c r="U68" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>128</v>
       </c>
       <c r="V68" s="5">
@@ -9098,11 +9675,11 @@
       <c r="W68" s="5"/>
       <c r="X68" s="16"/>
       <c r="Y68" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="Z68" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2.402061855670103</v>
       </c>
       <c r="AA68" s="1">
@@ -9128,16 +9705,25 @@
       </c>
       <c r="AH68" s="20"/>
       <c r="AI68" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>42</v>
       </c>
       <c r="AJ68" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK68" s="1"/>
-      <c r="AL68" s="1"/>
-      <c r="AM68" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK68" s="1">
+        <f t="shared" si="12"/>
+        <v>6.4020000000000001</v>
+      </c>
+      <c r="AL68" s="1">
+        <f t="shared" si="13"/>
+        <v>9.4379999999999971</v>
+      </c>
+      <c r="AM68" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN68" s="1"/>
       <c r="AO68" s="1"/>
       <c r="AP68" s="1"/>
@@ -9182,11 +9768,11 @@
         <v>62</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-32</v>
       </c>
       <c r="M69" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="N69" s="1"/>
@@ -9197,12 +9783,12 @@
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
       <c r="S69" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="T69" s="5"/>
       <c r="U69" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V69" s="5">
@@ -9211,11 +9797,11 @@
       <c r="W69" s="5"/>
       <c r="X69" s="16"/>
       <c r="Y69" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>25.01</v>
       </c>
       <c r="Z69" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>25.01</v>
       </c>
       <c r="AA69" s="1">
@@ -9241,16 +9827,25 @@
       </c>
       <c r="AH69" s="20"/>
       <c r="AI69" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ69" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK69" s="1"/>
-      <c r="AL69" s="1"/>
-      <c r="AM69" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK69" s="1">
+        <f t="shared" si="12"/>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="AL69" s="1">
+        <f t="shared" si="13"/>
+        <v>24.424000000000003</v>
+      </c>
+      <c r="AM69" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN69" s="1"/>
       <c r="AO69" s="1"/>
       <c r="AP69" s="1"/>
@@ -9295,11 +9890,11 @@
         <v>132</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="18">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="22">E70-K70</f>
         <v>-73</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" ref="M70:M101" si="19">E70-N70</f>
+        <f t="shared" ref="M70:M101" si="23">E70-N70</f>
         <v>59</v>
       </c>
       <c r="N70" s="1"/>
@@ -9310,12 +9905,12 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1">
-        <f t="shared" ref="S70:S101" si="20">M70/5</f>
+        <f t="shared" ref="S70:S101" si="24">M70/5</f>
         <v>11.8</v>
       </c>
       <c r="T70" s="5"/>
       <c r="U70" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V70" s="5">
@@ -9324,11 +9919,11 @@
       <c r="W70" s="5"/>
       <c r="X70" s="16"/>
       <c r="Y70" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>27.627118644067796</v>
       </c>
       <c r="Z70" s="1">
-        <f t="shared" ref="Z70:Z101" si="21">(F70+O70+P70+Q70+R70)/S70</f>
+        <f t="shared" ref="Z70:Z101" si="25">(F70+O70+P70+Q70+R70)/S70</f>
         <v>27.627118644067796</v>
       </c>
       <c r="AA70" s="1">
@@ -9354,16 +9949,25 @@
       </c>
       <c r="AH70" s="20"/>
       <c r="AI70" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ70" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AK70" s="1"/>
-      <c r="AL70" s="1"/>
-      <c r="AM70" s="1"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK70" s="1">
+        <f t="shared" si="12"/>
+        <v>4.13</v>
+      </c>
+      <c r="AL70" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM70" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AN70" s="1"/>
       <c r="AO70" s="1"/>
       <c r="AP70" s="1"/>
@@ -9408,11 +10012,11 @@
         <v>400</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-47</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>347</v>
       </c>
       <c r="N71" s="1">
@@ -9425,12 +10029,12 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
       <c r="S71" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>69.400000000000006</v>
       </c>
       <c r="T71" s="5"/>
       <c r="U71" s="5">
-        <f t="shared" ref="U71:U117" si="22">T71</f>
+        <f t="shared" ref="U71:U117" si="26">T71</f>
         <v>0</v>
       </c>
       <c r="V71" s="5">
@@ -9439,11 +10043,11 @@
       <c r="W71" s="5"/>
       <c r="X71" s="16"/>
       <c r="Y71" s="1">
-        <f t="shared" ref="Y71:Y117" si="23">(F71+O71+P71+Q71+R71+U71)/S71</f>
+        <f t="shared" ref="Y71:Y117" si="27">(F71+O71+P71+Q71+R71+U71)/S71</f>
         <v>17.630752737752157</v>
       </c>
       <c r="Z71" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>17.630752737752157</v>
       </c>
       <c r="AA71" s="1">
@@ -9469,16 +10073,25 @@
       </c>
       <c r="AH71" s="20"/>
       <c r="AI71" s="1">
-        <f t="shared" ref="AI71:AI117" si="24">ROUND(G71*V71,0)</f>
+        <f t="shared" ref="AI71:AI117" si="28">ROUND(G71*V71,0)</f>
         <v>0</v>
       </c>
       <c r="AJ71" s="1">
-        <f t="shared" ref="AJ71:AJ117" si="25">ROUND(G71*W71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AK71" s="1"/>
-      <c r="AL71" s="1"/>
-      <c r="AM71" s="1"/>
+        <f t="shared" ref="AJ71:AJ117" si="29">ROUND(G71*W71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK71" s="1">
+        <f t="shared" ref="AK71:AK117" si="30">S71*G71</f>
+        <v>24.29</v>
+      </c>
+      <c r="AL71" s="1">
+        <f t="shared" ref="AL71:AL117" si="31">P71*G71</f>
+        <v>57.250983999999995</v>
+      </c>
+      <c r="AM71" s="1">
+        <f t="shared" ref="AM71:AM117" si="32">R71*G71</f>
+        <v>0</v>
+      </c>
       <c r="AN71" s="1"/>
       <c r="AO71" s="1"/>
       <c r="AP71" s="1"/>
@@ -9519,11 +10132,11 @@
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M72" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N72" s="1"/>
@@ -9534,12 +10147,12 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
       <c r="S72" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="T72" s="5"/>
       <c r="U72" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V72" s="5">
@@ -9548,11 +10161,11 @@
       <c r="W72" s="5"/>
       <c r="X72" s="16"/>
       <c r="Y72" s="1" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z72" s="1" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA72" s="1">
@@ -9578,16 +10191,25 @@
       </c>
       <c r="AH72" s="20"/>
       <c r="AI72" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ72" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK72" s="1"/>
-      <c r="AL72" s="1"/>
-      <c r="AM72" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK72" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AL72" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM72" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN72" s="1"/>
       <c r="AO72" s="1"/>
       <c r="AP72" s="1"/>
@@ -9632,11 +10254,11 @@
         <v>16.2</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.21499999999999986</v>
       </c>
       <c r="M73" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>16.414999999999999</v>
       </c>
       <c r="N73" s="1"/>
@@ -9647,12 +10269,12 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
       <c r="S73" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>3.2829999999999999</v>
       </c>
       <c r="T73" s="5"/>
       <c r="U73" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V73" s="5">
@@ -9661,11 +10283,11 @@
       <c r="W73" s="5"/>
       <c r="X73" s="16"/>
       <c r="Y73" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>19.04599451720987</v>
       </c>
       <c r="Z73" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>19.04599451720987</v>
       </c>
       <c r="AA73" s="1">
@@ -9693,16 +10315,25 @@
         <v>126</v>
       </c>
       <c r="AI73" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ73" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK73" s="1"/>
-      <c r="AL73" s="1"/>
-      <c r="AM73" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK73" s="1">
+        <f t="shared" si="30"/>
+        <v>3.2829999999999999</v>
+      </c>
+      <c r="AL73" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM73" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN73" s="1"/>
       <c r="AO73" s="1"/>
       <c r="AP73" s="1"/>
@@ -9747,11 +10378,11 @@
         <v>4036.52</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-12.230999999999767</v>
       </c>
       <c r="M74" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>3622.8190000000004</v>
       </c>
       <c r="N74" s="1">
@@ -9766,11 +10397,11 @@
         <v>274.3805727064348</v>
       </c>
       <c r="S74" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>724.56380000000013</v>
       </c>
       <c r="T74" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>3516.9179637070029</v>
       </c>
       <c r="U74" s="5">
@@ -9785,11 +10416,11 @@
       </c>
       <c r="X74" s="16"/>
       <c r="Y74" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12.276028142725322</v>
       </c>
       <c r="Z74" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>7.146158331803214</v>
       </c>
       <c r="AA74" s="1">
@@ -9815,16 +10446,25 @@
       </c>
       <c r="AH74" s="20"/>
       <c r="AI74" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1517</v>
       </c>
       <c r="AJ74" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>2200</v>
       </c>
-      <c r="AK74" s="1"/>
-      <c r="AL74" s="1"/>
-      <c r="AM74" s="1"/>
+      <c r="AK74" s="1">
+        <f t="shared" si="30"/>
+        <v>724.56380000000013</v>
+      </c>
+      <c r="AL74" s="1">
+        <f t="shared" si="31"/>
+        <v>655.72306358656454</v>
+      </c>
+      <c r="AM74" s="1">
+        <f t="shared" si="32"/>
+        <v>274.3805727064348</v>
+      </c>
       <c r="AN74" s="1"/>
       <c r="AO74" s="1"/>
       <c r="AP74" s="1"/>
@@ -9869,11 +10509,11 @@
         <v>218</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-5</v>
       </c>
       <c r="M75" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>213</v>
       </c>
       <c r="N75" s="1"/>
@@ -9884,15 +10524,15 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
       <c r="S75" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>42.6</v>
       </c>
       <c r="T75" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>90.200000000000045</v>
       </c>
       <c r="U75" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>90.200000000000045</v>
       </c>
       <c r="V75" s="5">
@@ -9901,11 +10541,11 @@
       <c r="W75" s="5"/>
       <c r="X75" s="16"/>
       <c r="Y75" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z75" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>9.8826291079812201</v>
       </c>
       <c r="AA75" s="1">
@@ -9931,16 +10571,25 @@
       </c>
       <c r="AH75" s="20"/>
       <c r="AI75" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>27</v>
       </c>
       <c r="AJ75" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK75" s="1"/>
-      <c r="AL75" s="1"/>
-      <c r="AM75" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK75" s="1">
+        <f t="shared" si="30"/>
+        <v>12.78</v>
+      </c>
+      <c r="AL75" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM75" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN75" s="1"/>
       <c r="AO75" s="1"/>
       <c r="AP75" s="1"/>
@@ -9985,11 +10634,11 @@
         <v>1829.2</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-79.634000000000015</v>
       </c>
       <c r="M76" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1749.566</v>
       </c>
       <c r="N76" s="1"/>
@@ -10002,15 +10651,15 @@
         <v>300.29472754319988</v>
       </c>
       <c r="S76" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>349.91320000000002</v>
       </c>
       <c r="T76" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1131.7221710400008</v>
       </c>
       <c r="U76" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>1131.7221710400008</v>
       </c>
       <c r="V76" s="5">
@@ -10021,11 +10670,11 @@
       </c>
       <c r="X76" s="16"/>
       <c r="Y76" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z76" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>8.7657059778253554</v>
       </c>
       <c r="AA76" s="1">
@@ -10051,16 +10700,25 @@
       </c>
       <c r="AH76" s="20"/>
       <c r="AI76" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>432</v>
       </c>
       <c r="AJ76" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>700</v>
       </c>
-      <c r="AK76" s="1"/>
-      <c r="AL76" s="1"/>
-      <c r="AM76" s="1"/>
+      <c r="AK76" s="1">
+        <f t="shared" si="30"/>
+        <v>349.91320000000002</v>
+      </c>
+      <c r="AL76" s="1">
+        <f t="shared" si="31"/>
+        <v>717.65350141679983</v>
+      </c>
+      <c r="AM76" s="1">
+        <f t="shared" si="32"/>
+        <v>300.29472754319988</v>
+      </c>
       <c r="AN76" s="1"/>
       <c r="AO76" s="1"/>
       <c r="AP76" s="1"/>
@@ -10105,11 +10763,11 @@
         <v>4130.5</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-16.716999999999643</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>4113.7830000000004</v>
       </c>
       <c r="N77" s="1"/>
@@ -10122,11 +10780,11 @@
         <v>856.66229999999996</v>
       </c>
       <c r="S77" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>822.75660000000005</v>
       </c>
       <c r="T77" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>2179.3251999999993</v>
       </c>
       <c r="U77" s="5">
@@ -10141,11 +10799,11 @@
       </c>
       <c r="X77" s="16"/>
       <c r="Y77" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12.850798401374112</v>
       </c>
       <c r="Z77" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>9.3511908625224045</v>
       </c>
       <c r="AA77" s="1">
@@ -10171,16 +10829,25 @@
       </c>
       <c r="AH77" s="20"/>
       <c r="AI77" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>879</v>
       </c>
       <c r="AJ77" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>2000</v>
       </c>
-      <c r="AK77" s="1"/>
-      <c r="AL77" s="1"/>
-      <c r="AM77" s="1"/>
+      <c r="AK77" s="1">
+        <f t="shared" si="30"/>
+        <v>822.75660000000005</v>
+      </c>
+      <c r="AL77" s="1">
+        <f t="shared" si="31"/>
+        <v>2047.2777000000001</v>
+      </c>
+      <c r="AM77" s="1">
+        <f t="shared" si="32"/>
+        <v>856.66229999999996</v>
+      </c>
       <c r="AN77" s="1"/>
       <c r="AO77" s="1"/>
       <c r="AP77" s="1"/>
@@ -10225,11 +10892,11 @@
         <v>3690.9369999999999</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-94.205999999999676</v>
       </c>
       <c r="M78" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>3299.1940000000004</v>
       </c>
       <c r="N78" s="1">
@@ -10244,11 +10911,11 @@
         <v>523.70897167764247</v>
       </c>
       <c r="S78" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>659.83880000000011</v>
       </c>
       <c r="T78" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>969.88695024528079</v>
       </c>
       <c r="U78" s="5">
@@ -10263,11 +10930,11 @@
       </c>
       <c r="X78" s="16"/>
       <c r="Y78" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12.909313001902889</v>
       </c>
       <c r="Z78" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>10.530115309610045</v>
       </c>
       <c r="AA78" s="1">
@@ -10293,16 +10960,25 @@
       </c>
       <c r="AH78" s="20"/>
       <c r="AI78" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>370</v>
       </c>
       <c r="AJ78" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1200</v>
       </c>
-      <c r="AK78" s="1"/>
-      <c r="AL78" s="1"/>
-      <c r="AM78" s="1"/>
+      <c r="AK78" s="1">
+        <f t="shared" si="30"/>
+        <v>659.83880000000011</v>
+      </c>
+      <c r="AL78" s="1">
+        <f t="shared" si="31"/>
+        <v>1251.575678077078</v>
+      </c>
+      <c r="AM78" s="1">
+        <f t="shared" si="32"/>
+        <v>523.70897167764247</v>
+      </c>
       <c r="AN78" s="1"/>
       <c r="AO78" s="1"/>
       <c r="AP78" s="1"/>
@@ -10347,11 +11023,11 @@
         <v>10.85</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1.3250000000000011</v>
       </c>
       <c r="M79" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>12.175000000000001</v>
       </c>
       <c r="N79" s="1"/>
@@ -10362,12 +11038,12 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>2.4350000000000001</v>
       </c>
       <c r="T79" s="5"/>
       <c r="U79" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V79" s="5">
@@ -10376,11 +11052,11 @@
       <c r="W79" s="5"/>
       <c r="X79" s="16"/>
       <c r="Y79" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>91.39917864476385</v>
       </c>
       <c r="Z79" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>91.39917864476385</v>
       </c>
       <c r="AA79" s="1">
@@ -10406,16 +11082,25 @@
       </c>
       <c r="AH79" s="20"/>
       <c r="AI79" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ79" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK79" s="1"/>
-      <c r="AL79" s="1"/>
-      <c r="AM79" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK79" s="1">
+        <f t="shared" si="30"/>
+        <v>2.4350000000000001</v>
+      </c>
+      <c r="AL79" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM79" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN79" s="1"/>
       <c r="AO79" s="1"/>
       <c r="AP79" s="1"/>
@@ -10456,11 +11141,11 @@
         <v>5.8</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.89500000000000046</v>
       </c>
       <c r="M80" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>6.6950000000000003</v>
       </c>
       <c r="N80" s="1"/>
@@ -10471,12 +11156,12 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>1.339</v>
       </c>
       <c r="T80" s="5"/>
       <c r="U80" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V80" s="5">
@@ -10485,11 +11170,11 @@
       <c r="W80" s="5"/>
       <c r="X80" s="16"/>
       <c r="Y80" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>814.54742345033617</v>
       </c>
       <c r="Z80" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>814.54742345033617</v>
       </c>
       <c r="AA80" s="1">
@@ -10517,16 +11202,25 @@
         <v>185</v>
       </c>
       <c r="AI80" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ80" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK80" s="1"/>
-      <c r="AL80" s="1"/>
-      <c r="AM80" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK80" s="1">
+        <f t="shared" si="30"/>
+        <v>1.339</v>
+      </c>
+      <c r="AL80" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM80" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN80" s="1"/>
       <c r="AO80" s="1"/>
       <c r="AP80" s="1"/>
@@ -10571,11 +11265,11 @@
         <v>145</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-23</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>122</v>
       </c>
       <c r="N81" s="1"/>
@@ -10586,15 +11280,15 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>24.4</v>
       </c>
       <c r="T81" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>35.799999999999955</v>
       </c>
       <c r="U81" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>35.799999999999955</v>
       </c>
       <c r="V81" s="5">
@@ -10603,11 +11297,11 @@
       <c r="W81" s="5"/>
       <c r="X81" s="16"/>
       <c r="Y81" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>11.999999999999998</v>
       </c>
       <c r="Z81" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>10.532786885245903</v>
       </c>
       <c r="AA81" s="1">
@@ -10633,16 +11327,25 @@
       </c>
       <c r="AH81" s="20"/>
       <c r="AI81" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>11</v>
       </c>
       <c r="AJ81" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK81" s="1"/>
-      <c r="AL81" s="1"/>
-      <c r="AM81" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK81" s="1">
+        <f t="shared" si="30"/>
+        <v>7.3199999999999994</v>
+      </c>
+      <c r="AL81" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM81" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN81" s="1"/>
       <c r="AO81" s="1"/>
       <c r="AP81" s="1"/>
@@ -10687,11 +11390,11 @@
         <v>37</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-3</v>
       </c>
       <c r="M82" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>34</v>
       </c>
       <c r="N82" s="1"/>
@@ -10702,15 +11405,15 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>6.8</v>
       </c>
       <c r="T82" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>10.599999999999994</v>
       </c>
       <c r="U82" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>10.599999999999994</v>
       </c>
       <c r="V82" s="5">
@@ -10719,11 +11422,11 @@
       <c r="W82" s="5"/>
       <c r="X82" s="16"/>
       <c r="Y82" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z82" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>10.441176470588236</v>
       </c>
       <c r="AA82" s="1">
@@ -10749,16 +11452,25 @@
       </c>
       <c r="AH82" s="20"/>
       <c r="AI82" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>3</v>
       </c>
       <c r="AJ82" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK82" s="1"/>
-      <c r="AL82" s="1"/>
-      <c r="AM82" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK82" s="1">
+        <f t="shared" si="30"/>
+        <v>2.04</v>
+      </c>
+      <c r="AL82" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM82" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN82" s="1"/>
       <c r="AO82" s="1"/>
       <c r="AP82" s="1"/>
@@ -10803,11 +11515,11 @@
         <v>111</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-13</v>
       </c>
       <c r="M83" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>98</v>
       </c>
       <c r="N83" s="1"/>
@@ -10818,15 +11530,15 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>19.600000000000001</v>
       </c>
       <c r="T83" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>85.481288000000006</v>
       </c>
       <c r="U83" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>85.481288000000006</v>
       </c>
       <c r="V83" s="5">
@@ -10835,11 +11547,11 @@
       <c r="W83" s="5"/>
       <c r="X83" s="16"/>
       <c r="Y83" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z83" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>7.6387097959183672</v>
       </c>
       <c r="AA83" s="1">
@@ -10865,16 +11577,25 @@
       </c>
       <c r="AH83" s="20"/>
       <c r="AI83" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>6</v>
       </c>
       <c r="AJ83" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK83" s="1"/>
-      <c r="AL83" s="1"/>
-      <c r="AM83" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK83" s="1">
+        <f t="shared" si="30"/>
+        <v>1.3720000000000003</v>
+      </c>
+      <c r="AL83" s="1">
+        <f t="shared" si="31"/>
+        <v>2.0103098400000019</v>
+      </c>
+      <c r="AM83" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN83" s="1"/>
       <c r="AO83" s="1"/>
       <c r="AP83" s="1"/>
@@ -10919,11 +11640,11 @@
         <v>54</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-15</v>
       </c>
       <c r="M84" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>39</v>
       </c>
       <c r="N84" s="1"/>
@@ -10934,12 +11655,12 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>7.8</v>
       </c>
       <c r="T84" s="5"/>
       <c r="U84" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V84" s="5">
@@ -10948,11 +11669,11 @@
       <c r="W84" s="5"/>
       <c r="X84" s="16"/>
       <c r="Y84" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>24.358974358974361</v>
       </c>
       <c r="Z84" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>24.358974358974361</v>
       </c>
       <c r="AA84" s="1">
@@ -10978,16 +11699,25 @@
       </c>
       <c r="AH84" s="20"/>
       <c r="AI84" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ84" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK84" s="1"/>
-      <c r="AL84" s="1"/>
-      <c r="AM84" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK84" s="1">
+        <f t="shared" si="30"/>
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="AL84" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM84" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN84" s="1"/>
       <c r="AO84" s="1"/>
       <c r="AP84" s="1"/>
@@ -11032,11 +11762,11 @@
         <v>59</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-24</v>
       </c>
       <c r="M85" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>35</v>
       </c>
       <c r="N85" s="1"/>
@@ -11047,12 +11777,12 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
       <c r="T85" s="5"/>
       <c r="U85" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V85" s="5">
@@ -11061,11 +11791,11 @@
       <c r="W85" s="5"/>
       <c r="X85" s="16"/>
       <c r="Y85" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>24.428571428571427</v>
       </c>
       <c r="Z85" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>24.428571428571427</v>
       </c>
       <c r="AA85" s="1">
@@ -11091,16 +11821,25 @@
       </c>
       <c r="AH85" s="20"/>
       <c r="AI85" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ85" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK85" s="1"/>
-      <c r="AL85" s="1"/>
-      <c r="AM85" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK85" s="1">
+        <f t="shared" si="30"/>
+        <v>0.49000000000000005</v>
+      </c>
+      <c r="AL85" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM85" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN85" s="1"/>
       <c r="AO85" s="1"/>
       <c r="AP85" s="1"/>
@@ -11143,11 +11882,11 @@
         <v>71</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-23</v>
       </c>
       <c r="M86" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>48</v>
       </c>
       <c r="N86" s="1"/>
@@ -11158,15 +11897,15 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
       <c r="S86" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>9.6</v>
       </c>
       <c r="T86" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>59.199999999999989</v>
       </c>
       <c r="U86" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>59.199999999999989</v>
       </c>
       <c r="V86" s="5">
@@ -11175,11 +11914,11 @@
       <c r="W86" s="5"/>
       <c r="X86" s="16"/>
       <c r="Y86" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z86" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>5.8333333333333339</v>
       </c>
       <c r="AA86" s="1">
@@ -11205,16 +11944,25 @@
       </c>
       <c r="AH86" s="20"/>
       <c r="AI86" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>3</v>
       </c>
       <c r="AJ86" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK86" s="1"/>
-      <c r="AL86" s="1"/>
-      <c r="AM86" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK86" s="1">
+        <f t="shared" si="30"/>
+        <v>0.48</v>
+      </c>
+      <c r="AL86" s="1">
+        <f t="shared" si="31"/>
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="AM86" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN86" s="1"/>
       <c r="AO86" s="1"/>
       <c r="AP86" s="1"/>
@@ -11257,11 +12005,11 @@
         <v>92</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-22</v>
       </c>
       <c r="M87" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>70</v>
       </c>
       <c r="N87" s="1"/>
@@ -11272,14 +12020,14 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
       <c r="S87" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>14</v>
       </c>
       <c r="T87" s="13">
         <v>0</v>
       </c>
       <c r="U87" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V87" s="5">
@@ -11288,11 +12036,11 @@
       <c r="W87" s="5"/>
       <c r="X87" s="16"/>
       <c r="Y87" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>7.7428571428571429</v>
       </c>
       <c r="Z87" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>7.7428571428571429</v>
       </c>
       <c r="AA87" s="1">
@@ -11320,16 +12068,25 @@
         <v>200</v>
       </c>
       <c r="AI87" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ87" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK87" s="1"/>
-      <c r="AL87" s="1"/>
-      <c r="AM87" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK87" s="1">
+        <f t="shared" si="30"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="AL87" s="1">
+        <f t="shared" si="31"/>
+        <v>5.4200000000000008</v>
+      </c>
+      <c r="AM87" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN87" s="1"/>
       <c r="AO87" s="1"/>
       <c r="AP87" s="1"/>
@@ -11374,11 +12131,11 @@
         <v>79</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-25</v>
       </c>
       <c r="M88" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>54</v>
       </c>
       <c r="N88" s="1"/>
@@ -11389,14 +12146,14 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
       <c r="S88" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>10.8</v>
       </c>
       <c r="T88" s="13">
         <v>0</v>
       </c>
       <c r="U88" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V88" s="5">
@@ -11405,11 +12162,11 @@
       <c r="W88" s="5"/>
       <c r="X88" s="16"/>
       <c r="Y88" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12.814814814814815</v>
       </c>
       <c r="Z88" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>12.814814814814815</v>
       </c>
       <c r="AA88" s="1">
@@ -11437,16 +12194,25 @@
         <v>200</v>
       </c>
       <c r="AI88" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ88" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK88" s="1"/>
-      <c r="AL88" s="1"/>
-      <c r="AM88" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK88" s="1">
+        <f t="shared" si="30"/>
+        <v>0.59400000000000008</v>
+      </c>
+      <c r="AL88" s="1">
+        <f t="shared" si="31"/>
+        <v>3.9820000000000002</v>
+      </c>
+      <c r="AM88" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN88" s="1"/>
       <c r="AO88" s="1"/>
       <c r="AP88" s="1"/>
@@ -11491,11 +12257,11 @@
         <v>20</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-2</v>
       </c>
       <c r="M89" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>18</v>
       </c>
       <c r="N89" s="1"/>
@@ -11506,12 +12272,12 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
       <c r="S89" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>3.6</v>
       </c>
       <c r="T89" s="5"/>
       <c r="U89" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V89" s="5">
@@ -11520,11 +12286,11 @@
       <c r="W89" s="5"/>
       <c r="X89" s="16"/>
       <c r="Y89" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>16.666666666666668</v>
       </c>
       <c r="Z89" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>16.666666666666668</v>
       </c>
       <c r="AA89" s="1">
@@ -11552,16 +12318,25 @@
         <v>126</v>
       </c>
       <c r="AI89" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ89" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK89" s="1"/>
-      <c r="AL89" s="1"/>
-      <c r="AM89" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK89" s="1">
+        <f t="shared" si="30"/>
+        <v>1.08</v>
+      </c>
+      <c r="AL89" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM89" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN89" s="1"/>
       <c r="AO89" s="1"/>
       <c r="AP89" s="1"/>
@@ -11606,11 +12381,11 @@
         <v>7.8</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1.5550000000000006</v>
       </c>
       <c r="M90" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>9.3550000000000004</v>
       </c>
       <c r="N90" s="1"/>
@@ -11621,12 +12396,12 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>1.871</v>
       </c>
       <c r="T90" s="5"/>
       <c r="U90" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V90" s="5">
@@ -11635,11 +12410,11 @@
       <c r="W90" s="5"/>
       <c r="X90" s="16"/>
       <c r="Y90" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>26.357028327097808</v>
       </c>
       <c r="Z90" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>26.357028327097808</v>
       </c>
       <c r="AA90" s="1">
@@ -11665,16 +12440,25 @@
       </c>
       <c r="AH90" s="20"/>
       <c r="AI90" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ90" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK90" s="1"/>
-      <c r="AL90" s="1"/>
-      <c r="AM90" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK90" s="1">
+        <f t="shared" si="30"/>
+        <v>1.871</v>
+      </c>
+      <c r="AL90" s="1">
+        <f t="shared" si="31"/>
+        <v>5.8570000000000011</v>
+      </c>
+      <c r="AM90" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN90" s="1"/>
       <c r="AO90" s="1"/>
       <c r="AP90" s="1"/>
@@ -11719,11 +12503,11 @@
         <v>51</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-30</v>
       </c>
       <c r="M91" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
       <c r="N91" s="1"/>
@@ -11734,15 +12518,15 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
       <c r="S91" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>4.2</v>
       </c>
       <c r="T91" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>7.0000000000000071</v>
       </c>
       <c r="U91" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>7.0000000000000071</v>
       </c>
       <c r="V91" s="5">
@@ -11751,11 +12535,11 @@
       <c r="W91" s="5"/>
       <c r="X91" s="16"/>
       <c r="Y91" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z91" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>10.333333333333332</v>
       </c>
       <c r="AA91" s="1">
@@ -11781,16 +12565,25 @@
       </c>
       <c r="AH91" s="20"/>
       <c r="AI91" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="AJ91" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK91" s="1"/>
-      <c r="AL91" s="1"/>
-      <c r="AM91" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK91" s="1">
+        <f t="shared" si="30"/>
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="AL91" s="1">
+        <f t="shared" si="31"/>
+        <v>4.6639999999999997</v>
+      </c>
+      <c r="AM91" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN91" s="1"/>
       <c r="AO91" s="1"/>
       <c r="AP91" s="1"/>
@@ -11835,11 +12628,11 @@
         <v>238</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-62</v>
       </c>
       <c r="M92" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>176</v>
       </c>
       <c r="N92" s="1"/>
@@ -11850,15 +12643,15 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
       <c r="S92" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>35.200000000000003</v>
       </c>
       <c r="T92" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>163.60000000000002</v>
       </c>
       <c r="U92" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>163.60000000000002</v>
       </c>
       <c r="V92" s="5">
@@ -11867,11 +12660,11 @@
       <c r="W92" s="5"/>
       <c r="X92" s="16"/>
       <c r="Y92" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z92" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>7.3522727272727266</v>
       </c>
       <c r="AA92" s="1">
@@ -11897,16 +12690,25 @@
       </c>
       <c r="AH92" s="20"/>
       <c r="AI92" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>13</v>
       </c>
       <c r="AJ92" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK92" s="1"/>
-      <c r="AL92" s="1"/>
-      <c r="AM92" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK92" s="1">
+        <f t="shared" si="30"/>
+        <v>2.8160000000000003</v>
+      </c>
+      <c r="AL92" s="1">
+        <f t="shared" si="31"/>
+        <v>10.704000000000001</v>
+      </c>
+      <c r="AM92" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN92" s="1"/>
       <c r="AO92" s="1"/>
       <c r="AP92" s="1"/>
@@ -11951,11 +12753,11 @@
         <v>100</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-16</v>
       </c>
       <c r="M93" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="N93" s="1"/>
@@ -11966,12 +12768,12 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>16.8</v>
       </c>
       <c r="T93" s="5"/>
       <c r="U93" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V93" s="5">
@@ -11980,11 +12782,11 @@
       <c r="W93" s="5"/>
       <c r="X93" s="16"/>
       <c r="Y93" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>22.44047619047619</v>
       </c>
       <c r="Z93" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>22.44047619047619</v>
       </c>
       <c r="AA93" s="1">
@@ -12010,16 +12812,25 @@
       </c>
       <c r="AH93" s="20"/>
       <c r="AI93" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ93" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK93" s="1"/>
-      <c r="AL93" s="1"/>
-      <c r="AM93" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK93" s="1">
+        <f t="shared" si="30"/>
+        <v>1.3440000000000001</v>
+      </c>
+      <c r="AL93" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM93" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN93" s="1"/>
       <c r="AO93" s="1"/>
       <c r="AP93" s="1"/>
@@ -12062,11 +12873,11 @@
         <v>42</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-17</v>
       </c>
       <c r="M94" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>25</v>
       </c>
       <c r="N94" s="1"/>
@@ -12077,7 +12888,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
       <c r="S94" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>5</v>
       </c>
       <c r="T94" s="5">
@@ -12085,7 +12896,7 @@
         <v>33</v>
       </c>
       <c r="U94" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>33</v>
       </c>
       <c r="V94" s="5">
@@ -12094,11 +12905,11 @@
       <c r="W94" s="5"/>
       <c r="X94" s="16"/>
       <c r="Y94" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>11</v>
       </c>
       <c r="Z94" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="AA94" s="1">
@@ -12124,16 +12935,25 @@
       </c>
       <c r="AH94" s="20"/>
       <c r="AI94" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>6</v>
       </c>
       <c r="AJ94" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK94" s="1"/>
-      <c r="AL94" s="1"/>
-      <c r="AM94" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK94" s="1">
+        <f t="shared" si="30"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="AL94" s="1">
+        <f t="shared" si="31"/>
+        <v>3.74</v>
+      </c>
+      <c r="AM94" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN94" s="1"/>
       <c r="AO94" s="1"/>
       <c r="AP94" s="1"/>
@@ -12178,11 +12998,11 @@
         <v>271.89999999999998</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-5.4679999999999609</v>
       </c>
       <c r="M95" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>266.43200000000002</v>
       </c>
       <c r="N95" s="1"/>
@@ -12193,15 +13013,15 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
       <c r="S95" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>53.2864</v>
       </c>
       <c r="T95" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>155.03179999999998</v>
       </c>
       <c r="U95" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>155.03179999999998</v>
       </c>
       <c r="V95" s="5">
@@ -12210,11 +13030,11 @@
       <c r="W95" s="5"/>
       <c r="X95" s="16"/>
       <c r="Y95" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>11.999999999999998</v>
       </c>
       <c r="Z95" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>9.0905934722555841</v>
       </c>
       <c r="AA95" s="1">
@@ -12240,16 +13060,25 @@
       </c>
       <c r="AH95" s="20"/>
       <c r="AI95" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>155</v>
       </c>
       <c r="AJ95" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK95" s="1"/>
-      <c r="AL95" s="1"/>
-      <c r="AM95" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK95" s="1">
+        <f t="shared" si="30"/>
+        <v>53.2864</v>
+      </c>
+      <c r="AL95" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM95" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN95" s="1"/>
       <c r="AO95" s="1"/>
       <c r="AP95" s="1"/>
@@ -12294,11 +13123,11 @@
         <v>74.400000000000006</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-0.18500000000000227</v>
       </c>
       <c r="M96" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>74.215000000000003</v>
       </c>
       <c r="N96" s="1"/>
@@ -12309,15 +13138,15 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
       <c r="S96" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>14.843</v>
       </c>
       <c r="T96" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>49.388999999999982</v>
       </c>
       <c r="U96" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>49.388999999999982</v>
       </c>
       <c r="V96" s="5">
@@ -12326,11 +13155,11 @@
       <c r="W96" s="5"/>
       <c r="X96" s="16"/>
       <c r="Y96" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>11.999999999999998</v>
       </c>
       <c r="Z96" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>8.6725729300006744</v>
       </c>
       <c r="AA96" s="1">
@@ -12356,16 +13185,25 @@
       </c>
       <c r="AH96" s="20"/>
       <c r="AI96" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>49</v>
       </c>
       <c r="AJ96" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK96" s="1"/>
-      <c r="AL96" s="1"/>
-      <c r="AM96" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK96" s="1">
+        <f t="shared" si="30"/>
+        <v>14.843</v>
+      </c>
+      <c r="AL96" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM96" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN96" s="1"/>
       <c r="AO96" s="1"/>
       <c r="AP96" s="1"/>
@@ -12410,11 +13248,11 @@
         <v>208.8</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-12.247000000000014</v>
       </c>
       <c r="M97" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>196.553</v>
       </c>
       <c r="N97" s="1"/>
@@ -12425,15 +13263,15 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
       <c r="S97" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>39.310600000000001</v>
       </c>
       <c r="T97" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>92.077200000000062</v>
       </c>
       <c r="U97" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>92.077200000000062</v>
       </c>
       <c r="V97" s="5">
@@ -12442,11 +13280,11 @@
       <c r="W97" s="5"/>
       <c r="X97" s="16"/>
       <c r="Y97" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z97" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>9.6577004675583673</v>
       </c>
       <c r="AA97" s="1">
@@ -12472,16 +13310,25 @@
       </c>
       <c r="AH97" s="20"/>
       <c r="AI97" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>92</v>
       </c>
       <c r="AJ97" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK97" s="1"/>
-      <c r="AL97" s="1"/>
-      <c r="AM97" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK97" s="1">
+        <f t="shared" si="30"/>
+        <v>39.310600000000001</v>
+      </c>
+      <c r="AL97" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM97" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN97" s="1"/>
       <c r="AO97" s="1"/>
       <c r="AP97" s="1"/>
@@ -12526,11 +13373,11 @@
         <v>39</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-26</v>
       </c>
       <c r="M98" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>13</v>
       </c>
       <c r="N98" s="1"/>
@@ -12541,12 +13388,12 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
       <c r="S98" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>2.6</v>
       </c>
       <c r="T98" s="5"/>
       <c r="U98" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V98" s="5">
@@ -12555,11 +13402,11 @@
       <c r="W98" s="5"/>
       <c r="X98" s="16"/>
       <c r="Y98" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>29</v>
       </c>
       <c r="Z98" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="AA98" s="1">
@@ -12585,16 +13432,25 @@
       </c>
       <c r="AH98" s="20"/>
       <c r="AI98" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ98" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK98" s="1"/>
-      <c r="AL98" s="1"/>
-      <c r="AM98" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK98" s="1">
+        <f t="shared" si="30"/>
+        <v>0.78</v>
+      </c>
+      <c r="AL98" s="1">
+        <f t="shared" si="31"/>
+        <v>4.6200000000000028</v>
+      </c>
+      <c r="AM98" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN98" s="1"/>
       <c r="AO98" s="1"/>
       <c r="AP98" s="1"/>
@@ -12633,11 +13489,11 @@
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M99" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N99" s="1"/>
@@ -12648,12 +13504,12 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
       <c r="S99" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="T99" s="5"/>
       <c r="U99" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V99" s="5">
@@ -12662,11 +13518,11 @@
       <c r="W99" s="5"/>
       <c r="X99" s="16"/>
       <c r="Y99" s="1" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z99" s="1" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA99" s="1">
@@ -12692,16 +13548,25 @@
       </c>
       <c r="AH99" s="20"/>
       <c r="AI99" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ99" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK99" s="1"/>
-      <c r="AL99" s="1"/>
-      <c r="AM99" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK99" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AL99" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM99" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN99" s="1"/>
       <c r="AO99" s="1"/>
       <c r="AP99" s="1"/>
@@ -12746,11 +13611,11 @@
         <v>362</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-28</v>
       </c>
       <c r="M100" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>334</v>
       </c>
       <c r="N100" s="1"/>
@@ -12761,15 +13626,15 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
       <c r="S100" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>66.8</v>
       </c>
       <c r="T100" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>77.675314000000185</v>
       </c>
       <c r="U100" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>77.675314000000185</v>
       </c>
       <c r="V100" s="5">
@@ -12778,11 +13643,11 @@
       <c r="W100" s="5"/>
       <c r="X100" s="16"/>
       <c r="Y100" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z100" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>10.837195898203589</v>
       </c>
       <c r="AA100" s="1">
@@ -12808,16 +13673,25 @@
       </c>
       <c r="AH100" s="20"/>
       <c r="AI100" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>22</v>
       </c>
       <c r="AJ100" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK100" s="1"/>
-      <c r="AL100" s="1"/>
-      <c r="AM100" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK100" s="1">
+        <f t="shared" si="30"/>
+        <v>18.704000000000001</v>
+      </c>
+      <c r="AL100" s="1">
+        <f t="shared" si="31"/>
+        <v>4.1789120799999386</v>
+      </c>
+      <c r="AM100" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN100" s="1"/>
       <c r="AO100" s="1"/>
       <c r="AP100" s="1"/>
@@ -12860,11 +13734,11 @@
         <v>380</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-178</v>
       </c>
       <c r="M101" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>202</v>
       </c>
       <c r="N101" s="1"/>
@@ -12877,15 +13751,15 @@
         <v>80.90316</v>
       </c>
       <c r="S101" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>40.4</v>
       </c>
       <c r="T101" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>208.55199999999994</v>
       </c>
       <c r="U101" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>208.55199999999994</v>
       </c>
       <c r="V101" s="5">
@@ -12894,11 +13768,11 @@
       <c r="W101" s="5"/>
       <c r="X101" s="16"/>
       <c r="Y101" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z101" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>6.8378217821782181</v>
       </c>
       <c r="AA101" s="1">
@@ -12924,16 +13798,25 @@
       </c>
       <c r="AH101" s="20"/>
       <c r="AI101" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>58</v>
       </c>
       <c r="AJ101" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK101" s="1"/>
-      <c r="AL101" s="1"/>
-      <c r="AM101" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK101" s="1">
+        <f t="shared" si="30"/>
+        <v>11.312000000000001</v>
+      </c>
+      <c r="AL101" s="1">
+        <f t="shared" si="31"/>
+        <v>54.136555200000004</v>
+      </c>
+      <c r="AM101" s="1">
+        <f t="shared" si="32"/>
+        <v>22.652884800000002</v>
+      </c>
       <c r="AN101" s="1"/>
       <c r="AO101" s="1"/>
       <c r="AP101" s="1"/>
@@ -12978,11 +13861,11 @@
         <v>478</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L117" si="26">E102-K102</f>
+        <f t="shared" ref="L102:L117" si="33">E102-K102</f>
         <v>-45</v>
       </c>
       <c r="M102" s="1">
-        <f t="shared" ref="M102:M117" si="27">E102-N102</f>
+        <f t="shared" ref="M102:M117" si="34">E102-N102</f>
         <v>433</v>
       </c>
       <c r="N102" s="1"/>
@@ -12993,15 +13876,15 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
       <c r="S102" s="1">
-        <f t="shared" ref="S102:S117" si="28">M102/5</f>
+        <f t="shared" ref="S102:S117" si="35">M102/5</f>
         <v>86.6</v>
       </c>
       <c r="T102" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>13.026741999999786</v>
       </c>
       <c r="U102" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>13.026741999999786</v>
       </c>
       <c r="V102" s="5">
@@ -13010,11 +13893,11 @@
       <c r="W102" s="5"/>
       <c r="X102" s="16"/>
       <c r="Y102" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>11.999999999999998</v>
       </c>
       <c r="Z102" s="1">
-        <f t="shared" ref="Z102:Z117" si="29">(F102+O102+P102+Q102+R102)/S102</f>
+        <f t="shared" ref="Z102:Z117" si="36">(F102+O102+P102+Q102+R102)/S102</f>
         <v>11.84957572748268</v>
       </c>
       <c r="AA102" s="1">
@@ -13040,16 +13923,25 @@
       </c>
       <c r="AH102" s="20"/>
       <c r="AI102" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>4</v>
       </c>
       <c r="AJ102" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK102" s="1"/>
-      <c r="AL102" s="1"/>
-      <c r="AM102" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK102" s="1">
+        <f t="shared" si="30"/>
+        <v>24.248000000000001</v>
+      </c>
+      <c r="AL102" s="1">
+        <f t="shared" si="31"/>
+        <v>47.928512240000003</v>
+      </c>
+      <c r="AM102" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN102" s="1"/>
       <c r="AO102" s="1"/>
       <c r="AP102" s="1"/>
@@ -13092,11 +13984,11 @@
         <v>26</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M103" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>26</v>
       </c>
       <c r="N103" s="1"/>
@@ -13107,15 +13999,15 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
       <c r="S103" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>5.2</v>
       </c>
       <c r="T103" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>16.400000000000006</v>
       </c>
       <c r="U103" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>16.400000000000006</v>
       </c>
       <c r="V103" s="5">
@@ -13124,11 +14016,11 @@
       <c r="W103" s="5"/>
       <c r="X103" s="16"/>
       <c r="Y103" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z103" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>8.8461538461538467</v>
       </c>
       <c r="AA103" s="1">
@@ -13154,16 +14046,25 @@
       </c>
       <c r="AH103" s="20"/>
       <c r="AI103" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="AJ103" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK103" s="1"/>
-      <c r="AL103" s="1"/>
-      <c r="AM103" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK103" s="1">
+        <f t="shared" si="30"/>
+        <v>0.46799999999999997</v>
+      </c>
+      <c r="AL103" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM103" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN103" s="1"/>
       <c r="AO103" s="1"/>
       <c r="AP103" s="1"/>
@@ -13208,11 +14109,11 @@
         <v>42.5</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0.68500000000000227</v>
       </c>
       <c r="M104" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>43.185000000000002</v>
       </c>
       <c r="N104" s="1"/>
@@ -13223,12 +14124,12 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
       <c r="S104" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>8.6370000000000005</v>
       </c>
       <c r="T104" s="5"/>
       <c r="U104" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V104" s="5">
@@ -13237,11 +14138,11 @@
       <c r="W104" s="5"/>
       <c r="X104" s="16"/>
       <c r="Y104" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>16.520203774458725</v>
       </c>
       <c r="Z104" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>16.520203774458725</v>
       </c>
       <c r="AA104" s="1">
@@ -13267,16 +14168,25 @@
       </c>
       <c r="AH104" s="20"/>
       <c r="AI104" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ104" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK104" s="1"/>
-      <c r="AL104" s="1"/>
-      <c r="AM104" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK104" s="1">
+        <f t="shared" si="30"/>
+        <v>8.6370000000000005</v>
+      </c>
+      <c r="AL104" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM104" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN104" s="1"/>
       <c r="AO104" s="1"/>
       <c r="AP104" s="1"/>
@@ -13321,11 +14231,11 @@
         <v>58.8</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>-11.233999999999995</v>
       </c>
       <c r="M105" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>47.566000000000003</v>
       </c>
       <c r="N105" s="1"/>
@@ -13336,12 +14246,12 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
       <c r="S105" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>9.5132000000000012</v>
       </c>
       <c r="T105" s="5"/>
       <c r="U105" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V105" s="5">
@@ -13350,11 +14260,11 @@
       <c r="W105" s="5"/>
       <c r="X105" s="16"/>
       <c r="Y105" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>28.573350712693937</v>
       </c>
       <c r="Z105" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>28.573350712693937</v>
       </c>
       <c r="AA105" s="1">
@@ -13380,16 +14290,25 @@
       </c>
       <c r="AH105" s="20"/>
       <c r="AI105" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ105" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK105" s="1"/>
-      <c r="AL105" s="1"/>
-      <c r="AM105" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK105" s="1">
+        <f t="shared" si="30"/>
+        <v>9.5132000000000012</v>
+      </c>
+      <c r="AL105" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM105" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN105" s="1"/>
       <c r="AO105" s="1"/>
       <c r="AP105" s="1"/>
@@ -13432,11 +14351,11 @@
         <v>15</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M106" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>15</v>
       </c>
       <c r="N106" s="1"/>
@@ -13447,12 +14366,12 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
       <c r="S106" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
       <c r="T106" s="5"/>
       <c r="U106" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V106" s="5">
@@ -13461,11 +14380,11 @@
       <c r="W106" s="5"/>
       <c r="X106" s="16"/>
       <c r="Y106" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>19</v>
       </c>
       <c r="Z106" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>19</v>
       </c>
       <c r="AA106" s="1">
@@ -13493,16 +14412,25 @@
         <v>126</v>
       </c>
       <c r="AI106" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ106" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK106" s="1"/>
-      <c r="AL106" s="1"/>
-      <c r="AM106" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK106" s="1">
+        <f t="shared" si="30"/>
+        <v>0.27</v>
+      </c>
+      <c r="AL106" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM106" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN106" s="1"/>
       <c r="AO106" s="1"/>
       <c r="AP106" s="1"/>
@@ -13545,11 +14473,11 @@
         <v>16</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M107" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>16</v>
       </c>
       <c r="N107" s="1"/>
@@ -13560,12 +14488,12 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
       <c r="S107" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>3.2</v>
       </c>
       <c r="T107" s="5"/>
       <c r="U107" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V107" s="5">
@@ -13574,11 +14502,11 @@
       <c r="W107" s="5"/>
       <c r="X107" s="16"/>
       <c r="Y107" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>13.125</v>
       </c>
       <c r="Z107" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>13.125</v>
       </c>
       <c r="AA107" s="1">
@@ -13604,16 +14532,25 @@
       </c>
       <c r="AH107" s="20"/>
       <c r="AI107" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ107" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK107" s="1"/>
-      <c r="AL107" s="1"/>
-      <c r="AM107" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK107" s="1">
+        <f t="shared" si="30"/>
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="AL107" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM107" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN107" s="1"/>
       <c r="AO107" s="1"/>
       <c r="AP107" s="1"/>
@@ -13656,11 +14593,11 @@
         <v>3.9</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>-3.9</v>
       </c>
       <c r="M108" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N108" s="1"/>
@@ -13671,7 +14608,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
       <c r="S108" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T108" s="5"/>
@@ -13686,11 +14623,11 @@
         <v>150</v>
       </c>
       <c r="Y108" s="1" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z108" s="1" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA108" s="1">
@@ -13716,16 +14653,25 @@
       </c>
       <c r="AH108" s="20"/>
       <c r="AI108" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>100</v>
       </c>
       <c r="AJ108" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK108" s="1"/>
-      <c r="AL108" s="1"/>
-      <c r="AM108" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK108" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AL108" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM108" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN108" s="1"/>
       <c r="AO108" s="1"/>
       <c r="AP108" s="1"/>
@@ -13770,11 +14716,11 @@
         <v>530.23800000000006</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>21.4849999999999</v>
       </c>
       <c r="M109" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>551.72299999999996</v>
       </c>
       <c r="N109" s="1"/>
@@ -13787,15 +14733,15 @@
         <v>86.367563000000018</v>
       </c>
       <c r="S109" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>110.34459999999999</v>
       </c>
       <c r="T109" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>527.20479999999964</v>
       </c>
       <c r="U109" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>527.20479999999964</v>
       </c>
       <c r="V109" s="5">
@@ -13806,11 +14752,11 @@
       </c>
       <c r="X109" s="16"/>
       <c r="Y109" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>11.999999999999998</v>
       </c>
       <c r="Z109" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>7.222196645780584</v>
       </c>
       <c r="AA109" s="1">
@@ -13836,16 +14782,25 @@
       </c>
       <c r="AH109" s="20"/>
       <c r="AI109" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>227</v>
       </c>
       <c r="AJ109" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
-      <c r="AK109" s="1"/>
-      <c r="AL109" s="1"/>
-      <c r="AM109" s="1"/>
+      <c r="AK109" s="1">
+        <f t="shared" si="30"/>
+        <v>110.34459999999999</v>
+      </c>
+      <c r="AL109" s="1">
+        <f t="shared" si="31"/>
+        <v>206.4038370000001</v>
+      </c>
+      <c r="AM109" s="1">
+        <f t="shared" si="32"/>
+        <v>86.367563000000018</v>
+      </c>
       <c r="AN109" s="1"/>
       <c r="AO109" s="1"/>
       <c r="AP109" s="1"/>
@@ -13888,11 +14843,11 @@
         <v>20.8</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>-11.294</v>
       </c>
       <c r="M110" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>9.5060000000000002</v>
       </c>
       <c r="N110" s="1"/>
@@ -13903,7 +14858,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
       <c r="S110" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>1.9012</v>
       </c>
       <c r="T110" s="5"/>
@@ -13918,11 +14873,11 @@
         <v>200</v>
       </c>
       <c r="Y110" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>137.03871239217338</v>
       </c>
       <c r="Z110" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>84.44035346097202</v>
       </c>
       <c r="AA110" s="1">
@@ -13948,16 +14903,25 @@
       </c>
       <c r="AH110" s="20"/>
       <c r="AI110" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>100</v>
       </c>
       <c r="AJ110" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK110" s="1"/>
-      <c r="AL110" s="1"/>
-      <c r="AM110" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK110" s="1">
+        <f t="shared" si="30"/>
+        <v>1.9012</v>
+      </c>
+      <c r="AL110" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM110" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN110" s="1"/>
       <c r="AO110" s="1"/>
       <c r="AP110" s="1"/>
@@ -14004,11 +14968,11 @@
         <v>57.5</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>415.50700000000001</v>
       </c>
       <c r="M111" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>473.00700000000001</v>
       </c>
       <c r="N111" s="1"/>
@@ -14019,12 +14983,12 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
       <c r="S111" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>94.601399999999998</v>
       </c>
       <c r="T111" s="5"/>
       <c r="U111" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V111" s="5">
@@ -14033,11 +14997,11 @@
       <c r="W111" s="5"/>
       <c r="X111" s="16"/>
       <c r="Y111" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>20.667442553704277</v>
       </c>
       <c r="Z111" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>20.667442553704277</v>
       </c>
       <c r="AA111" s="1">
@@ -14065,16 +15029,25 @@
         <v>255</v>
       </c>
       <c r="AI111" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ111" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK111" s="1"/>
-      <c r="AL111" s="1"/>
-      <c r="AM111" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK111" s="1">
+        <f t="shared" si="30"/>
+        <v>94.601399999999998</v>
+      </c>
+      <c r="AL111" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM111" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN111" s="1"/>
       <c r="AO111" s="1"/>
       <c r="AP111" s="1"/>
@@ -14119,11 +15092,11 @@
         <v>235</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>-57</v>
       </c>
       <c r="M112" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>178</v>
       </c>
       <c r="N112" s="1"/>
@@ -14134,15 +15107,15 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
       <c r="S112" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>35.6</v>
       </c>
       <c r="T112" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>150.20000000000005</v>
       </c>
       <c r="U112" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>150.20000000000005</v>
       </c>
       <c r="V112" s="5">
@@ -14151,11 +15124,11 @@
       <c r="W112" s="5"/>
       <c r="X112" s="16"/>
       <c r="Y112" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z112" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>7.7808988764044944</v>
       </c>
       <c r="AA112" s="1">
@@ -14181,16 +15154,25 @@
       </c>
       <c r="AH112" s="20"/>
       <c r="AI112" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>45</v>
       </c>
       <c r="AJ112" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK112" s="1"/>
-      <c r="AL112" s="1"/>
-      <c r="AM112" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK112" s="1">
+        <f t="shared" si="30"/>
+        <v>10.68</v>
+      </c>
+      <c r="AL112" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM112" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN112" s="1"/>
       <c r="AO112" s="1"/>
       <c r="AP112" s="1"/>
@@ -14235,11 +15217,11 @@
         <v>150</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>-19</v>
       </c>
       <c r="M113" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>131</v>
       </c>
       <c r="N113" s="1"/>
@@ -14250,15 +15232,15 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
       <c r="S113" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>26.2</v>
       </c>
       <c r="T113" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>174.59999999999997</v>
       </c>
       <c r="U113" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>174.59999999999997</v>
       </c>
       <c r="V113" s="5">
@@ -14267,11 +15249,11 @@
       <c r="W113" s="5"/>
       <c r="X113" s="16"/>
       <c r="Y113" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z113" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>5.3358778625954209</v>
       </c>
       <c r="AA113" s="1">
@@ -14297,16 +15279,25 @@
       </c>
       <c r="AH113" s="20"/>
       <c r="AI113" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>52</v>
       </c>
       <c r="AJ113" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK113" s="1"/>
-      <c r="AL113" s="1"/>
-      <c r="AM113" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK113" s="1">
+        <f t="shared" si="30"/>
+        <v>7.8599999999999994</v>
+      </c>
+      <c r="AL113" s="1">
+        <f t="shared" si="31"/>
+        <v>23.340000000000003</v>
+      </c>
+      <c r="AM113" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN113" s="1"/>
       <c r="AO113" s="1"/>
       <c r="AP113" s="1"/>
@@ -14351,11 +15342,11 @@
         <v>88.5</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>3.3299999999999983</v>
       </c>
       <c r="M114" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>91.83</v>
       </c>
       <c r="N114" s="1"/>
@@ -14366,15 +15357,15 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
       <c r="S114" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>18.366</v>
       </c>
       <c r="T114" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>127.01520000000002</v>
       </c>
       <c r="U114" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>127.01520000000002</v>
       </c>
       <c r="V114" s="5">
@@ -14383,11 +15374,11 @@
       <c r="W114" s="5"/>
       <c r="X114" s="16"/>
       <c r="Y114" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z114" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>5.084220842861809</v>
       </c>
       <c r="AA114" s="1">
@@ -14413,16 +15404,25 @@
       </c>
       <c r="AH114" s="20"/>
       <c r="AI114" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>127</v>
       </c>
       <c r="AJ114" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK114" s="1"/>
-      <c r="AL114" s="1"/>
-      <c r="AM114" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK114" s="1">
+        <f t="shared" si="30"/>
+        <v>18.366</v>
+      </c>
+      <c r="AL114" s="1">
+        <f t="shared" si="31"/>
+        <v>15.64979999999998</v>
+      </c>
+      <c r="AM114" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN114" s="1"/>
       <c r="AO114" s="1"/>
       <c r="AP114" s="1"/>
@@ -14467,11 +15467,11 @@
         <v>44</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>-12</v>
       </c>
       <c r="M115" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>32</v>
       </c>
       <c r="N115" s="1"/>
@@ -14482,12 +15482,12 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
       <c r="S115" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>6.4</v>
       </c>
       <c r="T115" s="5"/>
       <c r="U115" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V115" s="5">
@@ -14496,11 +15496,11 @@
       <c r="W115" s="5"/>
       <c r="X115" s="16"/>
       <c r="Y115" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>26.09375</v>
       </c>
       <c r="Z115" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>26.09375</v>
       </c>
       <c r="AA115" s="1">
@@ -14526,16 +15526,25 @@
       </c>
       <c r="AH115" s="20"/>
       <c r="AI115" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ115" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK115" s="1"/>
-      <c r="AL115" s="1"/>
-      <c r="AM115" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK115" s="1">
+        <f t="shared" si="30"/>
+        <v>1.92</v>
+      </c>
+      <c r="AL115" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM115" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN115" s="1"/>
       <c r="AO115" s="1"/>
       <c r="AP115" s="1"/>
@@ -14580,11 +15589,11 @@
         <v>25</v>
       </c>
       <c r="L116" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>-4</v>
       </c>
       <c r="M116" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>21</v>
       </c>
       <c r="N116" s="1"/>
@@ -14595,15 +15604,15 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
       <c r="S116" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>4.2</v>
       </c>
       <c r="T116" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>12.400000000000006</v>
       </c>
       <c r="U116" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>12.400000000000006</v>
       </c>
       <c r="V116" s="5">
@@ -14612,11 +15621,11 @@
       <c r="W116" s="5"/>
       <c r="X116" s="16"/>
       <c r="Y116" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="Z116" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>9.0476190476190474</v>
       </c>
       <c r="AA116" s="1">
@@ -14642,16 +15651,25 @@
       </c>
       <c r="AH116" s="20"/>
       <c r="AI116" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="AJ116" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK116" s="1"/>
-      <c r="AL116" s="1"/>
-      <c r="AM116" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK116" s="1">
+        <f t="shared" si="30"/>
+        <v>0.504</v>
+      </c>
+      <c r="AL116" s="1">
+        <f t="shared" si="31"/>
+        <v>5.76</v>
+      </c>
+      <c r="AM116" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN116" s="1"/>
       <c r="AO116" s="1"/>
       <c r="AP116" s="1"/>
@@ -14688,11 +15706,11 @@
       <c r="J117" s="1"/>
       <c r="K117" s="1"/>
       <c r="L117" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M117" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N117" s="1"/>
@@ -14703,12 +15721,12 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
       <c r="S117" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T117" s="5"/>
       <c r="U117" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V117" s="5">
@@ -14717,11 +15735,11 @@
       <c r="W117" s="5"/>
       <c r="X117" s="16"/>
       <c r="Y117" s="1" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z117" s="1" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA117" s="1">
@@ -14747,16 +15765,25 @@
       </c>
       <c r="AH117" s="20"/>
       <c r="AI117" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AJ117" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AK117" s="1"/>
-      <c r="AL117" s="1"/>
-      <c r="AM117" s="1"/>
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AK117" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AL117" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AM117" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AN117" s="1"/>
       <c r="AO117" s="1"/>
       <c r="AP117" s="1"/>

--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ КИ/дв 02,07,26 днрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ КИ/дв 02,07,26 днрсч пок ки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\02,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1952B62A-316A-4F35-8712-4227B6803DA5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2419B0E2-001D-46E0-B5FE-FD22F8C2DFCB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="270">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -1545,7 +1545,9 @@
       <c r="V3" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="W3" s="3"/>
+      <c r="W3" s="3" t="s">
+        <v>259</v>
+      </c>
       <c r="X3" s="3" t="s">
         <v>257</v>
       </c>
